--- a/Smile_Kids_Grades_Master_Backup.xlsx
+++ b/Smile_Kids_Grades_Master_Backup.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q174"/>
+  <dimension ref="A1:Q173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -600,7 +600,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>إجمالي الطلاب: 170 طالب • العام الدراسي 2026/2027 • موحد مع بوابات المعلمات والكنترول الإداري</t>
+          <t>إجمالي الطلاب: 169 طالب • العام الدراسي 2026/2027 • موحد مع بوابات المعلمات والكنترول الإداري</t>
         </is>
       </c>
     </row>
@@ -4672,17 +4672,17 @@
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>SK-G2-LN-013</t>
+          <t>SK-G2-LN-020</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>ليان محمد أمين</t>
+          <t>ليان محمود أمين</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>Layan Mohamed Amin</t>
+          <t>Layan Mahmoud Amin</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>SK-G2-LN-020</t>
+          <t>SK-G2-AR-006</t>
         </is>
       </c>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>ليان محمود أمين</t>
+          <t>لين مهند خضرو</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>Layan Mahmoud Amin</t>
+          <t>Leen Mohannad Khidro</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G59" s="13" t="n">
@@ -4822,17 +4822,17 @@
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>SK-G2-AR-006</t>
+          <t>SK-G2-LN-008</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>لين مهند خضرو</t>
+          <t>مالك أحمد عبد المؤمن</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>Leen Mohannad Khidro</t>
+          <t>Malek Ahmed Abdel Moemen</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G60" s="13" t="n">
@@ -4897,17 +4897,17 @@
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>SK-G2-LN-008</t>
+          <t>SK-G2-AR-005</t>
         </is>
       </c>
       <c r="C61" s="14" t="inlineStr">
         <is>
-          <t>مالك أحمد عبد المؤمن</t>
+          <t>مالك محمد الخشن</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>Malek Ahmed Abdel Moemen</t>
+          <t>Malek Mohamed El-Khoshen</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G61" s="13" t="n">
@@ -4972,17 +4972,17 @@
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>SK-G2-AR-005</t>
+          <t>SK-G2-LN-021</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>مالك محمد الخشن</t>
+          <t>محمد أحمد ضاحي</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>Malek Mohamed El-Khoshen</t>
+          <t>Mohamed Ahmed Dhahi</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G62" s="13" t="n">
@@ -5047,17 +5047,17 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>SK-G2-LN-021</t>
+          <t>SK-G2-LN-004</t>
         </is>
       </c>
       <c r="C63" s="14" t="inlineStr">
         <is>
-          <t>محمد أحمد ضاحي</t>
+          <t>معتز محمد عطاها</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Ahmed Dhahi</t>
+          <t>Moataz Mohamed Ataha</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
@@ -5122,17 +5122,17 @@
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>SK-G2-LN-004</t>
+          <t>SK-G2-AR-001</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>معتز محمد عطاها</t>
+          <t>مهدي أحمد محمد</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>Moataz Mohamed Ataha</t>
+          <t>Mahdi Ahmed Mohamed</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G64" s="13" t="n">
@@ -5197,17 +5197,17 @@
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>SK-G2-AR-001</t>
+          <t>SK-G2-LN-001</t>
         </is>
       </c>
       <c r="C65" s="14" t="inlineStr">
         <is>
-          <t>مهدي أحمد محمد</t>
+          <t>نوح عبد الحميد سمير</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>Mahdi Ahmed Mohamed</t>
+          <t>Noah Abdel Hamid Samir</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G65" s="13" t="n">
@@ -5272,17 +5272,17 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>SK-G2-LN-001</t>
+          <t>SK-G2-LN-022</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>نوح عبد الحميد سمير</t>
+          <t>يزن حسام عطية</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>Noah Abdel Hamid Samir</t>
+          <t>Yazan Hossam Atteya</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
@@ -5347,22 +5347,22 @@
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>SK-G2-LN-022</t>
+          <t>SK-G3-LN-008</t>
         </is>
       </c>
       <c r="C67" s="14" t="inlineStr">
         <is>
-          <t>يزن حسام عطية</t>
+          <t>آدم خالد عبد الله</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>Yazan Hossam Atteya</t>
+          <t>Adam Khaled Abdullah</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>الصف 2</t>
+          <t>الصف 3</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -5422,17 +5422,17 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-008</t>
+          <t>SK-G3-LN-006</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>آدم خالد عبد الله</t>
+          <t>آدم محمد صبحي</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>Adam Khaled Abdullah</t>
+          <t>Adam Mohamed Sobhy</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
@@ -5497,17 +5497,17 @@
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-006</t>
+          <t>SK-G3-LN-002</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>آدم محمد صبحي</t>
+          <t>آسية أحمد مصطفى</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>Adam Mohamed Sobhy</t>
+          <t>Asiya Ahmed Mostafa</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-002</t>
+          <t>SK-G3-LN-009</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>آسية أحمد مصطفى</t>
+          <t>أدهم مصطفى وحيد</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>Asiya Ahmed Mostafa</t>
+          <t>Adham Mostafa Waheed</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
@@ -5647,17 +5647,17 @@
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-009</t>
+          <t>SK-G3-LN-003</t>
         </is>
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>أدهم مصطفى وحيد</t>
+          <t>أريام أحمد حسن</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>Adham Mostafa Waheed</t>
+          <t>Aryam Ahmed Hassan</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
@@ -5722,17 +5722,17 @@
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-003</t>
+          <t>SK-G3-AR-002</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>أريام أحمد حسن</t>
+          <t>أرين أشرف مجدى</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>Aryam Ahmed Hassan</t>
+          <t>Areen Ashraf Magdy</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G72" s="13" t="n">
@@ -5797,17 +5797,17 @@
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-AR-002</t>
+          <t>SK-G3-LN-015</t>
         </is>
       </c>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>أرين أشرف مجدى</t>
+          <t>أمين السيد أحمد</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>Areen Ashraf Magdy</t>
+          <t>Amin Elsayed Ahmed</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G73" s="13" t="n">
@@ -5872,17 +5872,17 @@
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-015</t>
+          <t>SK-G3-AR-003</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>أمين السيد أحمد</t>
+          <t>الفاتح عبد القادر محمد</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>Amin Elsayed Ahmed</t>
+          <t>Al-Fateh Abdel Qader Mohamed</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G74" s="13" t="n">
@@ -5947,17 +5947,17 @@
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-AR-003</t>
+          <t>SK-G3-LN-022</t>
         </is>
       </c>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>الفاتح عبد القادر محمد</t>
+          <t>تالين أحمد محمود</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>Al-Fateh Abdel Qader Mohamed</t>
+          <t>Taleen Ahmed Mahmoud</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G75" s="13" t="n">
@@ -6022,17 +6022,17 @@
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-022</t>
+          <t>SK-G3-LN-014</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>تالين أحمد محمود</t>
+          <t>رائد عبد الكريم بشير</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>Taleen Ahmed Mahmoud</t>
+          <t>Raed Abdel Karim Basheer</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
@@ -6097,17 +6097,17 @@
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-014</t>
+          <t>SK-G3-LN-021</t>
         </is>
       </c>
       <c r="C77" s="14" t="inlineStr">
         <is>
-          <t>رائد عبد الكريم بشير</t>
+          <t>ريتال محمد عسل</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>Raed Abdel Karim Basheer</t>
+          <t>Retal Mohamed Asal</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
@@ -6172,17 +6172,17 @@
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-021</t>
+          <t>SK-G3-LN-017</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>ريتال محمد عسل</t>
+          <t>ريمان جمال الحسين</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>Retal Mohamed Asal</t>
+          <t>Reman Gamal El-Hussein</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
@@ -6247,17 +6247,17 @@
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-017</t>
+          <t>SK-G3-LN-007</t>
         </is>
       </c>
       <c r="C79" s="14" t="inlineStr">
         <is>
-          <t>ريمان جمال الحسين</t>
+          <t>زين سليمان محمد</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>Reman Gamal El-Hussein</t>
+          <t>Zein Soliman Mohamed</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
@@ -6322,17 +6322,17 @@
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-007</t>
+          <t>SK-G3-LN-013</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>زين سليمان محمد</t>
+          <t>زين محمد نبيل نوار</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>Zein Soliman Mohamed</t>
+          <t>Zein Mohamed Nabil Nawar</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
@@ -6397,17 +6397,17 @@
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-013</t>
+          <t>SK-G3-LN-012</t>
         </is>
       </c>
       <c r="C81" s="14" t="inlineStr">
         <is>
-          <t>زين محمد نبيل نوار</t>
+          <t>شهم محمد أنور حرب</t>
         </is>
       </c>
       <c r="D81" s="15" t="inlineStr">
         <is>
-          <t>Zein Mohamed Nabil Nawar</t>
+          <t>Shahm Mohamed Anwar Harb</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
@@ -6472,17 +6472,17 @@
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-012</t>
+          <t>SK-G3-LN-011</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>شهم محمد أنور حرب</t>
+          <t>عبد الرحمن خالد رجب</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>Shahm Mohamed Anwar Harb</t>
+          <t>Abdel Rahman Khaled Ragab</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
@@ -6547,17 +6547,17 @@
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-011</t>
+          <t>SK-G3-AR-005</t>
         </is>
       </c>
       <c r="C83" s="14" t="inlineStr">
         <is>
-          <t>عبد الرحمن خالد رجب</t>
+          <t>عبد الرحمن طه حسين</t>
         </is>
       </c>
       <c r="D83" s="15" t="inlineStr">
         <is>
-          <t>Abdel Rahman Khaled Ragab</t>
+          <t>Abdel Rahman Taha Hussein</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G83" s="13" t="n">
@@ -6622,17 +6622,17 @@
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-AR-005</t>
+          <t>SK-G3-AR-004</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>عبد الرحمن طه حسين</t>
+          <t>عمر محمود عبد الوهاب</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>Abdel Rahman Taha Hussein</t>
+          <t>Omar Mahmoud Abdel Wahab</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
@@ -6697,17 +6697,17 @@
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-AR-004</t>
+          <t>SK-G3-AR-3636</t>
         </is>
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>عمر محمود عبد الوهاب</t>
+          <t>فريدة محمد النجار</t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
         <is>
-          <t>Omar Mahmoud Abdel Wahab</t>
+          <t>Farida Mohamed El-Naggar</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
@@ -6721,16 +6721,16 @@
         </is>
       </c>
       <c r="G85" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H85" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I85" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J85" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K85" s="13" t="inlineStr">
         <is>
@@ -6748,11 +6748,11 @@
         </is>
       </c>
       <c r="N85" s="16" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O85" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P85" s="16" t="inlineStr">
@@ -6772,17 +6772,17 @@
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-AR-3636</t>
+          <t>SK-G3-LN-004</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>فريدة محمد النجار</t>
+          <t>ليان سامح بسيوني</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>Farida Mohamed El-Naggar</t>
+          <t>Layan Sameh Basiouny</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
@@ -6792,20 +6792,20 @@
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G86" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="H86" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="I86" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="J86" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="K86" s="13" t="inlineStr">
         <is>
@@ -6823,11 +6823,11 @@
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O86" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="P86" s="16" t="inlineStr">
@@ -6847,17 +6847,17 @@
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-004</t>
+          <t>SK-G3-LN-001</t>
         </is>
       </c>
       <c r="C87" s="14" t="inlineStr">
         <is>
-          <t>ليان سامح بسيوني</t>
+          <t>لين محمد عبد الحليم</t>
         </is>
       </c>
       <c r="D87" s="15" t="inlineStr">
         <is>
-          <t>Layan Sameh Basiouny</t>
+          <t>Leen Mohamed Abdel Halim</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
@@ -6922,17 +6922,17 @@
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-001</t>
+          <t>SK-G3-LN-020</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>لين محمد عبد الحليم</t>
+          <t>مؤيد أحمد سيد</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>Leen Mohamed Abdel Halim</t>
+          <t>Moayad Ahmed Sayed</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
@@ -6997,17 +6997,17 @@
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-020</t>
+          <t>SK-G3-LN-005</t>
         </is>
       </c>
       <c r="C89" s="14" t="inlineStr">
         <is>
-          <t>مؤيد أحمد سيد</t>
+          <t>ماريا خالد فهمي</t>
         </is>
       </c>
       <c r="D89" s="15" t="inlineStr">
         <is>
-          <t>Moayad Ahmed Sayed</t>
+          <t>Maria Khaled Fahmy</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-005</t>
+          <t>SK-G3-LN-019</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>ماريا خالد فهمي</t>
+          <t>مالك محمود ابراهيم</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>Maria Khaled Fahmy</t>
+          <t>Malek Mahmoud Ibrahim</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
@@ -7147,17 +7147,17 @@
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-019</t>
+          <t>SK-G3-LN-018</t>
         </is>
       </c>
       <c r="C91" s="14" t="inlineStr">
         <is>
-          <t>مالك محمود ابراهيم</t>
+          <t>مصطفى عبد السلام مصطفى</t>
         </is>
       </c>
       <c r="D91" s="15" t="inlineStr">
         <is>
-          <t>Malek Mahmoud Ibrahim</t>
+          <t>Mostafa Abdel Salam Mostafa</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
@@ -7222,17 +7222,17 @@
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-018</t>
+          <t>SK-G3-AR-001</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>مصطفى عبد السلام مصطفى</t>
+          <t>مليكة محمد عادل</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>Mostafa Abdel Salam Mostafa</t>
+          <t>Malika Mohamed Adel</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G92" s="13" t="n">
@@ -7297,17 +7297,17 @@
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-AR-001</t>
+          <t>SK-G3-LN-016</t>
         </is>
       </c>
       <c r="C93" s="14" t="inlineStr">
         <is>
-          <t>مليكة محمد عادل</t>
+          <t>نور أحمد عصام</t>
         </is>
       </c>
       <c r="D93" s="15" t="inlineStr">
         <is>
-          <t>Malika Mohamed Adel</t>
+          <t>Nour Ahmed Essam</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G93" s="13" t="n">
@@ -7372,17 +7372,17 @@
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-016</t>
+          <t>SK-G3-AR-006</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>نور أحمد عصام</t>
+          <t>نور حماده عياد</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>Nour Ahmed Essam</t>
+          <t>Nour Hamada Ayyad</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G94" s="13" t="n">
@@ -7447,17 +7447,17 @@
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-AR-006</t>
+          <t>SK-G3-LN-010</t>
         </is>
       </c>
       <c r="C95" s="14" t="inlineStr">
         <is>
-          <t>نور حماده عياد</t>
+          <t>يوسف محمد عبد اللطيف</t>
         </is>
       </c>
       <c r="D95" s="15" t="inlineStr">
         <is>
-          <t>Nour Hamada Ayyad</t>
+          <t>Youssef Mohamed Abdel Latif</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G95" s="13" t="n">
@@ -7522,22 +7522,22 @@
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>SK-G3-LN-010</t>
+          <t>SK-G4-LN-003</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>يوسف محمد عبد اللطيف</t>
+          <t>آدم عمرو أسامة</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>Youssef Mohamed Abdel Latif</t>
+          <t>Adam Amr Osama</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>الصف 3</t>
+          <t>الصف 4</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
@@ -7557,23 +7557,17 @@
       <c r="J96" s="13" t="n">
         <v>19.5</v>
       </c>
-      <c r="K96" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L96" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M96" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K96" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L96" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M96" s="13" t="n">
+        <v>19.5</v>
       </c>
       <c r="N96" s="16" t="n">
-        <v>78</v>
+        <v>136.5</v>
       </c>
       <c r="O96" s="16" t="inlineStr">
         <is>
@@ -7597,17 +7591,17 @@
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-003</t>
+          <t>SK-G4-AR-003</t>
         </is>
       </c>
       <c r="C97" s="14" t="inlineStr">
         <is>
-          <t>آدم عمرو أسامة</t>
+          <t>جانتي السيد عبد الغني</t>
         </is>
       </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
-          <t>Adam Amr Osama</t>
+          <t>Janti Elsayed Abdel Ghani</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
@@ -7666,17 +7660,17 @@
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-AR-003</t>
+          <t>SK-G4-LN-013</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>جانتي السيد عبد الغني</t>
+          <t>جنة عمرو أبو المكارم</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>Janti Elsayed Abdel Ghani</t>
+          <t>Janna Amr Abo El-Makarim</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
@@ -7735,17 +7729,17 @@
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-013</t>
+          <t>SK-G4-LN-001</t>
         </is>
       </c>
       <c r="C99" s="14" t="inlineStr">
         <is>
-          <t>جنة عمرو أبو المكارم</t>
+          <t>حمزة أحمد عبد الحميد</t>
         </is>
       </c>
       <c r="D99" s="15" t="inlineStr">
         <is>
-          <t>Janna Amr Abo El-Makarim</t>
+          <t>Hamza Ahmed Abdel Hamid</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
@@ -7804,17 +7798,17 @@
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-001</t>
+          <t>SK-G4-LN-008</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>حمزة أحمد عبد الحميد</t>
+          <t>دانة السيد علي</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>Hamza Ahmed Abdel Hamid</t>
+          <t>Dana Elsayed Ali</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
@@ -7873,17 +7867,17 @@
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-008</t>
+          <t>SK-G4-LN-007</t>
         </is>
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>دانة السيد علي</t>
+          <t>ريان عبد الرحمن</t>
         </is>
       </c>
       <c r="D101" s="15" t="inlineStr">
         <is>
-          <t>Dana Elsayed Ali</t>
+          <t>Rayan Abdel Rahman</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
@@ -7942,17 +7936,17 @@
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-007</t>
+          <t>SK-G4-AR-006</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>ريان عبد الرحمن</t>
+          <t>عبد الله مروان الشيخ</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>Rayan Abdel Rahman</t>
+          <t>Abdullah Marwan El-Sheikh</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
@@ -7962,7 +7956,7 @@
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G102" s="13" t="n">
@@ -8011,17 +8005,17 @@
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-AR-006</t>
+          <t>SK-G4-AR-004</t>
         </is>
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
-          <t>عبد الله مروان الشيخ</t>
+          <t>على شريف على</t>
         </is>
       </c>
       <c r="D103" s="15" t="inlineStr">
         <is>
-          <t>Abdullah Marwan El-Sheikh</t>
+          <t>Ali Sherif Ali</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
@@ -8080,17 +8074,17 @@
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-AR-004</t>
+          <t>SK-G4-LN-005</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>على شريف على</t>
+          <t>عمر أحمد الجزيرى</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>Ali Sherif Ali</t>
+          <t>Omar Ahmed El-Gezeiry</t>
         </is>
       </c>
       <c r="E104" s="12" t="inlineStr">
@@ -8100,7 +8094,7 @@
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G104" s="13" t="n">
@@ -8149,17 +8143,17 @@
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-005</t>
+          <t>SK-G4-LN-011</t>
         </is>
       </c>
       <c r="C105" s="14" t="inlineStr">
         <is>
-          <t>عمر أحمد الجزيرى</t>
+          <t>فيروز هشام محمد</t>
         </is>
       </c>
       <c r="D105" s="15" t="inlineStr">
         <is>
-          <t>Omar Ahmed El-Gezeiry</t>
+          <t>Fayrouz Hesham Mohamed</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
@@ -8218,17 +8212,17 @@
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-011</t>
+          <t>SK-G4-AR-002</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>فيروز هشام محمد</t>
+          <t>كارما أحمد عطية</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>Fayrouz Hesham Mohamed</t>
+          <t>Karma Ahmed Attia</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
@@ -8238,7 +8232,7 @@
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G106" s="13" t="n">
@@ -8287,17 +8281,17 @@
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-AR-002</t>
+          <t>SK-G4-LN-009</t>
         </is>
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>كارما أحمد عطية</t>
+          <t>كارما محمد حسام</t>
         </is>
       </c>
       <c r="D107" s="15" t="inlineStr">
         <is>
-          <t>Karma Ahmed Attia</t>
+          <t>Karma Mohamed Hossam</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
@@ -8307,7 +8301,7 @@
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G107" s="13" t="n">
@@ -8356,17 +8350,17 @@
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-009</t>
+          <t>SK-G4-LN-012</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>كارما محمد حسام</t>
+          <t>لوجين وليد محمد</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>Karma Mohamed Hossam</t>
+          <t>Lojain Walid Mohamed</t>
         </is>
       </c>
       <c r="E108" s="12" t="inlineStr">
@@ -8425,17 +8419,17 @@
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-012</t>
+          <t>SK-G4-AR-005</t>
         </is>
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t>لوجين وليد محمد</t>
+          <t>محمد محمود الصياد</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
         <is>
-          <t>Lojain Walid Mohamed</t>
+          <t>Mohamed Mahmoud El-Sayad</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
@@ -8445,7 +8439,7 @@
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G109" s="13" t="n">
@@ -8494,17 +8488,17 @@
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-AR-005</t>
+          <t>SK-G4-AR-001</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>محمد محمود الصياد</t>
+          <t>مها رضوان تسون</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Mahmoud El-Sayad</t>
+          <t>Maha Radwan Tsoun</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">
@@ -8563,17 +8557,17 @@
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-AR-001</t>
+          <t>SK-G4-LN-002</t>
         </is>
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>مها رضوان تسون</t>
+          <t>مهيب جمال فتح الله</t>
         </is>
       </c>
       <c r="D111" s="15" t="inlineStr">
         <is>
-          <t>Maha Radwan Tsoun</t>
+          <t>Moheb Gamal Fathallah</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
@@ -8583,7 +8577,7 @@
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G111" s="13" t="n">
@@ -8632,17 +8626,17 @@
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-002</t>
+          <t>SK-G4-LN-010</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>مهيب جمال فتح الله</t>
+          <t>ميرا محمد عطاها</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>Moheb Gamal Fathallah</t>
+          <t>Mira Mohamed Ataha</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr">
@@ -8701,17 +8695,17 @@
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-010</t>
+          <t>SK-G4-LN-006</t>
         </is>
       </c>
       <c r="C113" s="14" t="inlineStr">
         <is>
-          <t>ميرا محمد عطاها</t>
+          <t>يحيي محمد فاروق</t>
         </is>
       </c>
       <c r="D113" s="15" t="inlineStr">
         <is>
-          <t>Mira Mohamed Ataha</t>
+          <t>Yahia Mohamed Farouk</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
@@ -8770,17 +8764,17 @@
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-006</t>
+          <t>SK-G4-LN-004</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>يحيي محمد فاروق</t>
+          <t>يوسف كمال محمد</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>Yahia Mohamed Farouk</t>
+          <t>Youssef Kamal Mohamed</t>
         </is>
       </c>
       <c r="E114" s="12" t="inlineStr">
@@ -8839,22 +8833,22 @@
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-004</t>
+          <t>SK-G5-LN-005</t>
         </is>
       </c>
       <c r="C115" s="14" t="inlineStr">
         <is>
-          <t>يوسف كمال محمد</t>
+          <t>أيسل محمد السعيد</t>
         </is>
       </c>
       <c r="D115" s="15" t="inlineStr">
         <is>
-          <t>Youssef Kamal Mohamed</t>
+          <t>Aysel Mohamed El-Saeed</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>الصف 4</t>
+          <t>الصف 5</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
@@ -8908,17 +8902,17 @@
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-005</t>
+          <t>SK-G5-AR-003</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>أيسل محمد السعيد</t>
+          <t>جودى مهند خضرو</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>Aysel Mohamed El-Saeed</t>
+          <t>Judi Mohannad Khidro</t>
         </is>
       </c>
       <c r="E116" s="12" t="inlineStr">
@@ -8928,36 +8922,36 @@
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G116" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H116" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I116" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J116" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K116" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="L116" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M116" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="N116" s="16" t="n">
-        <v>136.5</v>
+        <v>140</v>
       </c>
       <c r="O116" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P116" s="16" t="inlineStr">
@@ -8977,17 +8971,17 @@
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-003</t>
+          <t>SK-G5-AR-002</t>
         </is>
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>جودى مهند خضرو</t>
+          <t>جويرية أحمد عطيه</t>
         </is>
       </c>
       <c r="D117" s="15" t="inlineStr">
         <is>
-          <t>Judi Mohannad Khidro</t>
+          <t>Jowairia Ahmed Attia</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
@@ -9001,32 +8995,32 @@
         </is>
       </c>
       <c r="G117" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="H117" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="I117" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="J117" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="K117" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="L117" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="M117" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="N117" s="16" t="n">
-        <v>140</v>
+        <v>136.5</v>
       </c>
       <c r="O117" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="P117" s="16" t="inlineStr">
@@ -9046,17 +9040,17 @@
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-002</t>
+          <t>SK-G5-AR-006</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>جويرية أحمد عطيه</t>
+          <t>رفيدة خالد رجب</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>Jowairia Ahmed Attia</t>
+          <t>Rofayda Khaled Ragab</t>
         </is>
       </c>
       <c r="E118" s="12" t="inlineStr">
@@ -9115,17 +9109,17 @@
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-006</t>
+          <t>SK-G5-LN-004</t>
         </is>
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>رفيدة خالد رجب</t>
+          <t>رقية رضا عبد المقصود</t>
         </is>
       </c>
       <c r="D119" s="15" t="inlineStr">
         <is>
-          <t>Rofayda Khaled Ragab</t>
+          <t>Roqaya Reda Abdel Maqsoud</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
@@ -9135,7 +9129,7 @@
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G119" s="13" t="n">
@@ -9184,17 +9178,17 @@
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-004</t>
+          <t>SK-G5-LN-003</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>رقية رضا عبد المقصود</t>
+          <t>رودينة عبد الله السيد</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>Roqaya Reda Abdel Maqsoud</t>
+          <t>Rodaina Abdullah Sayed</t>
         </is>
       </c>
       <c r="E120" s="12" t="inlineStr">
@@ -9253,17 +9247,17 @@
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-003</t>
+          <t>SK-G5-AR-007</t>
         </is>
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>رودينة عبد الله السيد</t>
+          <t>زياد مصطفى فرج</t>
         </is>
       </c>
       <c r="D121" s="15" t="inlineStr">
         <is>
-          <t>Rodaina Abdullah Sayed</t>
+          <t>Ziad Mostafa Farag</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
@@ -9273,7 +9267,7 @@
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G121" s="13" t="n">
@@ -9322,17 +9316,17 @@
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-007</t>
+          <t>SK-G5-AR-009</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>زياد مصطفى فرج</t>
+          <t>سامح طه النقاش</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>Ziad Mostafa Farag</t>
+          <t>Sameh Taha El-Naqqash</t>
         </is>
       </c>
       <c r="E122" s="12" t="inlineStr">
@@ -9391,17 +9385,17 @@
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-009</t>
+          <t>SK-G5-LN-002</t>
         </is>
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>سامح طه النقاش</t>
+          <t>عائشة محمد علاء الدين</t>
         </is>
       </c>
       <c r="D123" s="15" t="inlineStr">
         <is>
-          <t>Sameh Taha El-Naqqash</t>
+          <t>Aisha Mohamed Alaa El-Din</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr">
@@ -9411,7 +9405,7 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G123" s="13" t="n">
@@ -9460,17 +9454,17 @@
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-002</t>
+          <t>SK-G5-AR-008</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>عائشة محمد علاء الدين</t>
+          <t>عبد الله محمود الصياد</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>Aisha Mohamed Alaa El-Din</t>
+          <t>Abdullah Mahmoud El-Sayad</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr">
@@ -9480,7 +9474,7 @@
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G124" s="13" t="n">
@@ -9529,17 +9523,17 @@
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-008</t>
+          <t>SK-G5-AR-001</t>
         </is>
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>عبد الله محمود الصياد</t>
+          <t>كيان محمود منصور</t>
         </is>
       </c>
       <c r="D125" s="15" t="inlineStr">
         <is>
-          <t>Abdullah Mahmoud El-Sayad</t>
+          <t>Kayan Mahmoud Mansour</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
@@ -9598,17 +9592,17 @@
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-001</t>
+          <t>SK-G5-LN-001</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>كيان محمود منصور</t>
+          <t>لينا أحمد شوقى</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>Kayan Mahmoud Mansour</t>
+          <t>Lina Ahmed Shawky</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
@@ -9618,7 +9612,7 @@
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G126" s="13" t="n">
@@ -9667,17 +9661,17 @@
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-001</t>
+          <t>SK-G5-AR-005</t>
         </is>
       </c>
       <c r="C127" s="14" t="inlineStr">
         <is>
-          <t>لينا أحمد شوقى</t>
+          <t>ليندا هشام أحمد</t>
         </is>
       </c>
       <c r="D127" s="15" t="inlineStr">
         <is>
-          <t>Lina Ahmed Shawky</t>
+          <t>Linda Hesham Ahmed</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
@@ -9687,7 +9681,7 @@
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G127" s="13" t="n">
@@ -9736,17 +9730,17 @@
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-005</t>
+          <t>SK-G5-LN-009</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>ليندا هشام أحمد</t>
+          <t>محمد أدهم حربي</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>Linda Hesham Ahmed</t>
+          <t>Mohamed Adham Harby</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
@@ -9756,7 +9750,7 @@
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G128" s="13" t="n">
@@ -9805,17 +9799,17 @@
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-009</t>
+          <t>SK-G5-LN-008</t>
         </is>
       </c>
       <c r="C129" s="14" t="inlineStr">
         <is>
-          <t>محمد أدهم حربي</t>
+          <t>محمد عمرو محمد</t>
         </is>
       </c>
       <c r="D129" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Adham Harby</t>
+          <t>Mohamed Amr Mohamed</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
@@ -9874,17 +9868,17 @@
       </c>
       <c r="B130" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-008</t>
+          <t>SK-G5-LN-007</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>محمد عمرو محمد</t>
+          <t>مريم حمدى أحمد</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Amr Mohamed</t>
+          <t>Mariam Hamdy Ahmed</t>
         </is>
       </c>
       <c r="E130" s="12" t="inlineStr">
@@ -9943,17 +9937,17 @@
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-007</t>
+          <t>SK-G5-AR-010</t>
         </is>
       </c>
       <c r="C131" s="14" t="inlineStr">
         <is>
-          <t>مريم حمدى أحمد</t>
+          <t>مصطفى أحمد مصطفى</t>
         </is>
       </c>
       <c r="D131" s="15" t="inlineStr">
         <is>
-          <t>Mariam Hamdy Ahmed</t>
+          <t>Mostafa Ahmed Mostafa</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
@@ -9963,7 +9957,7 @@
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G131" s="13" t="n">
@@ -10012,17 +10006,17 @@
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-010</t>
+          <t>SK-G5-AR-004</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>مصطفى أحمد مصطفى</t>
+          <t>ملك محمد</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>Mostafa Ahmed Mostafa</t>
+          <t>Malak Mohamed</t>
         </is>
       </c>
       <c r="E132" s="12" t="inlineStr">
@@ -10036,32 +10030,32 @@
         </is>
       </c>
       <c r="G132" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H132" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I132" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J132" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K132" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="L132" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M132" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="N132" s="16" t="n">
-        <v>136.5</v>
+        <v>140</v>
       </c>
       <c r="O132" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P132" s="16" t="inlineStr">
@@ -10081,17 +10075,17 @@
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-004</t>
+          <t>SK-G5-LN-006</t>
         </is>
       </c>
       <c r="C133" s="14" t="inlineStr">
         <is>
-          <t>ملك محمد</t>
+          <t>مليكة محمد نوار</t>
         </is>
       </c>
       <c r="D133" s="15" t="inlineStr">
         <is>
-          <t>Malak Mohamed</t>
+          <t>Malika Mohamed Nawar</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
@@ -10101,36 +10095,36 @@
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G133" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="H133" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="I133" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="J133" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="K133" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="L133" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="M133" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="N133" s="16" t="n">
-        <v>140</v>
+        <v>136.5</v>
       </c>
       <c r="O133" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="P133" s="16" t="inlineStr">
@@ -10150,22 +10144,22 @@
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-006</t>
+          <t>SK-G6-LN-005</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>مليكة محمد نوار</t>
+          <t>أروى محمد أحمد</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>Malika Mohamed Nawar</t>
+          <t>Arwa Mohamed Ahmed</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>الصف 5</t>
+          <t>الصف 6</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
@@ -10219,17 +10213,17 @@
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-005</t>
+          <t>SK-G6-AR-004</t>
         </is>
       </c>
       <c r="C135" s="14" t="inlineStr">
         <is>
-          <t>أروى محمد أحمد</t>
+          <t>أسيل حمد أحمد</t>
         </is>
       </c>
       <c r="D135" s="15" t="inlineStr">
         <is>
-          <t>Arwa Mohamed Ahmed</t>
+          <t>Aseel Hamad Ahmed</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr">
@@ -10239,7 +10233,7 @@
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G135" s="13" t="n">
@@ -10288,17 +10282,17 @@
       </c>
       <c r="B136" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-AR-004</t>
+          <t>SK-G6-LN-011</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>أسيل حمد أحمد</t>
+          <t>أفنان أحمد</t>
         </is>
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>Aseel Hamad Ahmed</t>
+          <t>Afnan Ahmed</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr">
@@ -10308,7 +10302,7 @@
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G136" s="13" t="n">
@@ -10357,17 +10351,17 @@
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-011</t>
+          <t>SK-G6-AR-003</t>
         </is>
       </c>
       <c r="C137" s="14" t="inlineStr">
         <is>
-          <t>أفنان أحمد</t>
+          <t>باسم حسن العمري</t>
         </is>
       </c>
       <c r="D137" s="15" t="inlineStr">
         <is>
-          <t>Afnan Ahmed</t>
+          <t>Bassem Hassan El-Omari</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
@@ -10377,7 +10371,7 @@
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G137" s="13" t="n">
@@ -10426,17 +10420,17 @@
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-AR-003</t>
+          <t>SK-G6-LN-002</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>باسم حسن العمري</t>
+          <t>سيف جمال إسماعيل</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>Bassem Hassan El-Omari</t>
+          <t>Seif Gamal Ismail</t>
         </is>
       </c>
       <c r="E138" s="12" t="inlineStr">
@@ -10446,7 +10440,7 @@
       </c>
       <c r="F138" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G138" s="13" t="n">
@@ -10495,17 +10489,17 @@
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-002</t>
+          <t>SK-G6-LN-010</t>
         </is>
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>سيف جمال إسماعيل</t>
+          <t>لارين أحمد الشوني</t>
         </is>
       </c>
       <c r="D139" s="15" t="inlineStr">
         <is>
-          <t>Seif Gamal Ismail</t>
+          <t>Lareen Ahmed El-Shouny</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
@@ -10564,17 +10558,17 @@
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-010</t>
+          <t>SK-G6-LN-009</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>لارين أحمد الشوني</t>
+          <t>لورين وليد محمد</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>Lareen Ahmed El-Shouny</t>
+          <t>Loreen Walid Mohamed</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr">
@@ -10633,17 +10627,17 @@
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-009</t>
+          <t>SK-G6-LN-008</t>
         </is>
       </c>
       <c r="C141" s="14" t="inlineStr">
         <is>
-          <t>لورين وليد محمد</t>
+          <t>ليان السيد على</t>
         </is>
       </c>
       <c r="D141" s="15" t="inlineStr">
         <is>
-          <t>Loreen Walid Mohamed</t>
+          <t>Layan Elsayed Ali</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr">
@@ -10702,17 +10696,17 @@
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-008</t>
+          <t>SK-G6-LN-006</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>ليان السيد على</t>
+          <t>ليليا مازن شلار</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>Layan Elsayed Ali</t>
+          <t>Lilia Mazen Shollar</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
@@ -10771,17 +10765,17 @@
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-006</t>
+          <t>SK-G6-AR-002</t>
         </is>
       </c>
       <c r="C143" s="14" t="inlineStr">
         <is>
-          <t>ليليا مازن شلار</t>
+          <t>لينا هشام أحمد</t>
         </is>
       </c>
       <c r="D143" s="15" t="inlineStr">
         <is>
-          <t>Lilia Mazen Shollar</t>
+          <t>Lina Hesham Ahmed</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
@@ -10791,36 +10785,36 @@
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G143" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H143" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I143" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J143" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K143" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="L143" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M143" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="N143" s="16" t="n">
-        <v>136.5</v>
+        <v>140</v>
       </c>
       <c r="O143" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P143" s="16" t="inlineStr">
@@ -10840,17 +10834,17 @@
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-AR-002</t>
+          <t>SK-G6-LN-007</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>لينا هشام أحمد</t>
+          <t>ماسة محمد أنور</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>Lina Hesham Ahmed</t>
+          <t>Massa Mohamed Anwar</t>
         </is>
       </c>
       <c r="E144" s="12" t="inlineStr">
@@ -10860,36 +10854,36 @@
       </c>
       <c r="F144" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G144" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="H144" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="I144" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="J144" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="K144" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="L144" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="M144" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="N144" s="16" t="n">
-        <v>140</v>
+        <v>136.5</v>
       </c>
       <c r="O144" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="P144" s="16" t="inlineStr">
@@ -10909,17 +10903,17 @@
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-007</t>
+          <t>SK-G6-LN-003</t>
         </is>
       </c>
       <c r="C145" s="14" t="inlineStr">
         <is>
-          <t>ماسة محمد أنور</t>
+          <t>مالك محمود عبد الحميد</t>
         </is>
       </c>
       <c r="D145" s="15" t="inlineStr">
         <is>
-          <t>Massa Mohamed Anwar</t>
+          <t>Malek Mahmoud Abdel Hamid</t>
         </is>
       </c>
       <c r="E145" s="12" t="inlineStr">
@@ -10978,17 +10972,17 @@
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-003</t>
+          <t>SK-G6-LN-001</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>مالك محمود عبد الحميد</t>
+          <t>محمد السيد سمير</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>Malek Mahmoud Abdel Hamid</t>
+          <t>Mohamed Elsayed Samir</t>
         </is>
       </c>
       <c r="E146" s="12" t="inlineStr">
@@ -11047,17 +11041,17 @@
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-001</t>
+          <t>SK-G6-LN-004</t>
         </is>
       </c>
       <c r="C147" s="14" t="inlineStr">
         <is>
-          <t>محمد السيد سمير</t>
+          <t>محمد مصطفى وحيد</t>
         </is>
       </c>
       <c r="D147" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Elsayed Samir</t>
+          <t>Mohamed Mostafa Waheed</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr">
@@ -11116,17 +11110,17 @@
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-004</t>
+          <t>SK-G6-AR-005</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr">
         <is>
-          <t>محمد مصطفى وحيد</t>
+          <t>هدى محمد مجدى</t>
         </is>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Mostafa Waheed</t>
+          <t>Hoda Mohamed Magdy</t>
         </is>
       </c>
       <c r="E148" s="12" t="inlineStr">
@@ -11136,7 +11130,7 @@
       </c>
       <c r="F148" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G148" s="13" t="n">
@@ -11185,17 +11179,17 @@
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-AR-005</t>
+          <t>SK-G6-AR-001</t>
         </is>
       </c>
       <c r="C149" s="14" t="inlineStr">
         <is>
-          <t>هدى محمد مجدى</t>
+          <t>ياسين إسلام حمد</t>
         </is>
       </c>
       <c r="D149" s="15" t="inlineStr">
         <is>
-          <t>Hoda Mohamed Magdy</t>
+          <t>Yaseen Islam Hamad</t>
         </is>
       </c>
       <c r="E149" s="12" t="inlineStr">
@@ -11254,27 +11248,27 @@
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-AR-001</t>
+          <t>SK-G7-LN-008</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr">
         <is>
-          <t>ياسين إسلام حمد</t>
+          <t>آدم عبد الحميد عيد</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>Yaseen Islam Hamad</t>
+          <t>Adam Abdel Hamid Eid</t>
         </is>
       </c>
       <c r="E150" s="12" t="inlineStr">
         <is>
-          <t>الصف 6</t>
+          <t>الصف 7</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G150" s="13" t="n">
@@ -11323,17 +11317,17 @@
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-008</t>
+          <t>SK-G7-AR-006</t>
         </is>
       </c>
       <c r="C151" s="14" t="inlineStr">
         <is>
-          <t>آدم عبد الحميد عيد</t>
+          <t>بلال محمد عادل</t>
         </is>
       </c>
       <c r="D151" s="15" t="inlineStr">
         <is>
-          <t>Adam Abdel Hamid Eid</t>
+          <t>Belal Mohamed Adel</t>
         </is>
       </c>
       <c r="E151" s="12" t="inlineStr">
@@ -11343,7 +11337,7 @@
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G151" s="13" t="n">
@@ -11392,17 +11386,17 @@
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-AR-006</t>
+          <t>SK-G7-LN-003</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr">
         <is>
-          <t>بلال محمد عادل</t>
+          <t>تقى أحمد محمود</t>
         </is>
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>Belal Mohamed Adel</t>
+          <t>Toqa Ahmed Mahmoud</t>
         </is>
       </c>
       <c r="E152" s="12" t="inlineStr">
@@ -11412,7 +11406,7 @@
       </c>
       <c r="F152" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G152" s="13" t="n">
@@ -11461,17 +11455,17 @@
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-003</t>
+          <t>SK-G7-LN-004</t>
         </is>
       </c>
       <c r="C153" s="14" t="inlineStr">
         <is>
-          <t>تقى أحمد محمود</t>
+          <t>جودى خالد رجب</t>
         </is>
       </c>
       <c r="D153" s="15" t="inlineStr">
         <is>
-          <t>Toqa Ahmed Mahmoud</t>
+          <t>Judy Khaled Ragab</t>
         </is>
       </c>
       <c r="E153" s="12" t="inlineStr">
@@ -11530,17 +11524,17 @@
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-004</t>
+          <t>SK-G7-AR-004</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr">
         <is>
-          <t>جودى خالد رجب</t>
+          <t>سارة أحمد مصطفى</t>
         </is>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>Judy Khaled Ragab</t>
+          <t>Sara Ahmed Mostafa</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr">
@@ -11550,7 +11544,7 @@
       </c>
       <c r="F154" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G154" s="13" t="n">
@@ -11599,17 +11593,17 @@
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-AR-004</t>
+          <t>SK-G7-AR-005</t>
         </is>
       </c>
       <c r="C155" s="14" t="inlineStr">
         <is>
-          <t>سارة أحمد مصطفى</t>
+          <t>عمار محمود سعد</t>
         </is>
       </c>
       <c r="D155" s="15" t="inlineStr">
         <is>
-          <t>Sara Ahmed Mostafa</t>
+          <t>Ammar Mahmoud Saad</t>
         </is>
       </c>
       <c r="E155" s="12" t="inlineStr">
@@ -11668,17 +11662,17 @@
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-AR-005</t>
+          <t>SK-G7-LN-007</t>
         </is>
       </c>
       <c r="C156" s="14" t="inlineStr">
         <is>
-          <t>عمار محمود سعد</t>
+          <t>عمر أحمد عصام</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>Ammar Mahmoud Saad</t>
+          <t>Omar Ahmed Essam</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr">
@@ -11688,7 +11682,7 @@
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G156" s="13" t="n">
@@ -11737,17 +11731,17 @@
       </c>
       <c r="B157" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-007</t>
+          <t>SK-G7-AR-003</t>
         </is>
       </c>
       <c r="C157" s="14" t="inlineStr">
         <is>
-          <t>عمر أحمد عصام</t>
+          <t>فريدة شريف رجب</t>
         </is>
       </c>
       <c r="D157" s="15" t="inlineStr">
         <is>
-          <t>Omar Ahmed Essam</t>
+          <t>Farida Sherif Ragab</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
@@ -11757,7 +11751,7 @@
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G157" s="13" t="n">
@@ -11806,17 +11800,17 @@
       </c>
       <c r="B158" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-AR-003</t>
+          <t>SK-G7-AR-002</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr">
         <is>
-          <t>فريدة شريف رجب</t>
+          <t>ليان محمود رزق</t>
         </is>
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>Farida Sherif Ragab</t>
+          <t>Layan Mahmoud Rezk</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
@@ -11875,17 +11869,17 @@
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-AR-002</t>
+          <t>SK-G7-LN-006</t>
         </is>
       </c>
       <c r="C159" s="14" t="inlineStr">
         <is>
-          <t>ليان محمود رزق</t>
+          <t>مالك أدهم حربي</t>
         </is>
       </c>
       <c r="D159" s="15" t="inlineStr">
         <is>
-          <t>Layan Mahmoud Rezk</t>
+          <t>Malek Adham Harby</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr">
@@ -11895,7 +11889,7 @@
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G159" s="13" t="n">
@@ -11944,17 +11938,17 @@
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-006</t>
+          <t>SK-G7-LN-001</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr">
         <is>
-          <t>مالك أدهم حربي</t>
+          <t>مايا هيثم رشوان</t>
         </is>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>Malek Adham Harby</t>
+          <t>Maya Haitham Rashwan</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
@@ -12013,17 +12007,17 @@
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-001</t>
+          <t>SK-G7-LN-002</t>
         </is>
       </c>
       <c r="C161" s="14" t="inlineStr">
         <is>
-          <t>مايا هيثم رشوان</t>
+          <t>مريم أدهم حربي</t>
         </is>
       </c>
       <c r="D161" s="15" t="inlineStr">
         <is>
-          <t>Maya Haitham Rashwan</t>
+          <t>Mariam Adham Harby</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr">
@@ -12082,17 +12076,17 @@
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-002</t>
+          <t>SK-G7-AR-001</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr">
         <is>
-          <t>مريم أدهم حربي</t>
+          <t>نورسان إسلام محمد</t>
         </is>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>Mariam Adham Harby</t>
+          <t>Noursan Islam Mohamed</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
@@ -12102,7 +12096,7 @@
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G162" s="13" t="n">
@@ -12151,17 +12145,17 @@
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-AR-001</t>
+          <t>SK-G7-LN-005</t>
         </is>
       </c>
       <c r="C163" s="14" t="inlineStr">
         <is>
-          <t>نورسان إسلام محمد</t>
+          <t>ياسين سليمان محمد</t>
         </is>
       </c>
       <c r="D163" s="15" t="inlineStr">
         <is>
-          <t>Noursan Islam Mohamed</t>
+          <t>Yaseen Soliman Mohamed</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
@@ -12171,7 +12165,7 @@
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G163" s="13" t="n">
@@ -12220,22 +12214,22 @@
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-005</t>
+          <t>SK-G8-LN-001</t>
         </is>
       </c>
       <c r="C164" s="14" t="inlineStr">
         <is>
-          <t>ياسين سليمان محمد</t>
+          <t>بسملة عبد الله سيد</t>
         </is>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>Yaseen Soliman Mohamed</t>
+          <t>Basmala Abdullah Sayed</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr">
         <is>
-          <t>الصف 7</t>
+          <t>الصف 8</t>
         </is>
       </c>
       <c r="F164" s="12" t="inlineStr">
@@ -12289,17 +12283,17 @@
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>SK-G8-LN-001</t>
+          <t>SK-G8-AR-002</t>
         </is>
       </c>
       <c r="C165" s="14" t="inlineStr">
         <is>
-          <t>بسملة عبد الله سيد</t>
+          <t>سجد محمود منصور</t>
         </is>
       </c>
       <c r="D165" s="15" t="inlineStr">
         <is>
-          <t>Basmala Abdullah Sayed</t>
+          <t>Saged Mahmoud Mansour</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
@@ -12309,7 +12303,7 @@
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G165" s="13" t="n">
@@ -12358,17 +12352,17 @@
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t>SK-G8-AR-002</t>
+          <t>SK-G8-AR-003</t>
         </is>
       </c>
       <c r="C166" s="14" t="inlineStr">
         <is>
-          <t>سجد محمود منصور</t>
+          <t>عبد الغني عصام عبد الله</t>
         </is>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>Saged Mahmoud Mansour</t>
+          <t>Abdel Ghany Essam Abdullah</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr">
@@ -12427,17 +12421,17 @@
       </c>
       <c r="B167" s="13" t="inlineStr">
         <is>
-          <t>SK-G8-AR-003</t>
+          <t>SK-G8-AR-001</t>
         </is>
       </c>
       <c r="C167" s="14" t="inlineStr">
         <is>
-          <t>عبد الغني عصام عبد الله</t>
+          <t>محمد حسن العمري</t>
         </is>
       </c>
       <c r="D167" s="15" t="inlineStr">
         <is>
-          <t>Abdel Ghany Essam Abdullah</t>
+          <t>Mohamed Hassan El-Omari</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr">
@@ -12496,17 +12490,17 @@
       </c>
       <c r="B168" s="13" t="inlineStr">
         <is>
-          <t>SK-G8-AR-001</t>
+          <t>SK-G8-LN-002</t>
         </is>
       </c>
       <c r="C168" s="14" t="inlineStr">
         <is>
-          <t>محمد حسن العمري</t>
+          <t>وتين أحمد الشوني</t>
         </is>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Hassan El-Omari</t>
+          <t>Wateen Ahmed El-Shouny</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
@@ -12516,7 +12510,7 @@
       </c>
       <c r="F168" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G168" s="13" t="n">
@@ -12565,22 +12559,22 @@
       </c>
       <c r="B169" s="13" t="inlineStr">
         <is>
-          <t>SK-G8-LN-002</t>
+          <t>SK-G9-LN-001</t>
         </is>
       </c>
       <c r="C169" s="14" t="inlineStr">
         <is>
-          <t>وتين أحمد الشوني</t>
+          <t>أحمد رضا شوشة</t>
         </is>
       </c>
       <c r="D169" s="15" t="inlineStr">
         <is>
-          <t>Wateen Ahmed El-Shouny</t>
+          <t>Ahmed Reda Shousha</t>
         </is>
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>الصف 8</t>
+          <t>الصف 9</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
@@ -12634,17 +12628,17 @@
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
-          <t>SK-G9-LN-001</t>
+          <t>SK-G9-AR-002</t>
         </is>
       </c>
       <c r="C170" s="14" t="inlineStr">
         <is>
-          <t>أحمد رضا شوشة</t>
+          <t>أيمن عصام القاضي</t>
         </is>
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>Ahmed Reda Shousha</t>
+          <t>Ayman Essam El-Kady</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
@@ -12654,7 +12648,7 @@
       </c>
       <c r="F170" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G170" s="13" t="n">
@@ -12703,17 +12697,17 @@
       </c>
       <c r="B171" s="13" t="inlineStr">
         <is>
-          <t>SK-G9-AR-002</t>
+          <t>SK-G9-LN-002</t>
         </is>
       </c>
       <c r="C171" s="14" t="inlineStr">
         <is>
-          <t>أيمن عصام القاضي</t>
+          <t>جودى هيثم رشوان</t>
         </is>
       </c>
       <c r="D171" s="15" t="inlineStr">
         <is>
-          <t>Ayman Essam El-Kady</t>
+          <t>Judy Haitham Rashwan</t>
         </is>
       </c>
       <c r="E171" s="12" t="inlineStr">
@@ -12723,7 +12717,7 @@
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G171" s="13" t="n">
@@ -12772,17 +12766,17 @@
       </c>
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>SK-G9-LN-002</t>
+          <t>SK-G9-AR-001</t>
         </is>
       </c>
       <c r="C172" s="14" t="inlineStr">
         <is>
-          <t>جودى هيثم رشوان</t>
+          <t>ساره محمد عطاها</t>
         </is>
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>Judy Haitham Rashwan</t>
+          <t>Sara Mohamed Ataha</t>
         </is>
       </c>
       <c r="E172" s="12" t="inlineStr">
@@ -12792,7 +12786,7 @@
       </c>
       <c r="F172" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G172" s="13" t="n">
@@ -12841,17 +12835,17 @@
       </c>
       <c r="B173" s="13" t="inlineStr">
         <is>
-          <t>SK-G9-AR-001</t>
+          <t>SK-G9-AR-003</t>
         </is>
       </c>
       <c r="C173" s="14" t="inlineStr">
         <is>
-          <t>ساره محمد عطاها</t>
+          <t>محمد عبد الله النقاش</t>
         </is>
       </c>
       <c r="D173" s="15" t="inlineStr">
         <is>
-          <t>Sara Mohamed Ataha</t>
+          <t>Mohamed Abdullah El-Nakkash</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr">
@@ -12901,75 +12895,6 @@
       <c r="Q173" s="16" t="inlineStr">
         <is>
           <t>169</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="20" customHeight="1">
-      <c r="A174" s="12" t="n">
-        <v>170</v>
-      </c>
-      <c r="B174" s="13" t="inlineStr">
-        <is>
-          <t>SK-G9-AR-003</t>
-        </is>
-      </c>
-      <c r="C174" s="14" t="inlineStr">
-        <is>
-          <t>محمد عبد الله النقاش</t>
-        </is>
-      </c>
-      <c r="D174" s="15" t="inlineStr">
-        <is>
-          <t>Mohamed Abdullah El-Nakkash</t>
-        </is>
-      </c>
-      <c r="E174" s="12" t="inlineStr">
-        <is>
-          <t>الصف 9</t>
-        </is>
-      </c>
-      <c r="F174" s="12" t="inlineStr">
-        <is>
-          <t>عربي</t>
-        </is>
-      </c>
-      <c r="G174" s="13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="H174" s="13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="I174" s="13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J174" s="13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="K174" s="13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="L174" s="13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M174" s="13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="N174" s="16" t="n">
-        <v>136.5</v>
-      </c>
-      <c r="O174" s="16" t="inlineStr">
-        <is>
-          <t>97.5%</t>
-        </is>
-      </c>
-      <c r="P174" s="16" t="inlineStr">
-        <is>
-          <t>ممتاز 🌟</t>
-        </is>
-      </c>
-      <c r="Q174" s="16" t="inlineStr">
-        <is>
-          <t>170</t>
         </is>
       </c>
     </row>
@@ -12988,7 +12913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J171"/>
+  <dimension ref="A1:J170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15691,12 +15616,12 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>SK-G2-LN-013</t>
+          <t>SK-G2-LN-020</t>
         </is>
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>ليان محمد أمين</t>
+          <t>ليان محمود أمين</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -15741,12 +15666,12 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>SK-G2-LN-020</t>
+          <t>SK-G2-AR-006</t>
         </is>
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>ليان محمود أمين</t>
+          <t>لين مهند خضرو</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -15761,7 +15686,7 @@
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
@@ -15779,11 +15704,7 @@
           <t>مقيد ومنتظم</t>
         </is>
       </c>
-      <c r="J56" s="12" t="inlineStr">
-        <is>
-          <t>سجلات معتمدة 2026</t>
-        </is>
-      </c>
+      <c r="J56" s="12" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="12" t="n">
@@ -15791,12 +15712,12 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>SK-G2-AR-006</t>
+          <t>SK-G2-LN-008</t>
         </is>
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>لين مهند خضرو</t>
+          <t>مالك أحمد عبد المؤمن</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -15811,7 +15732,7 @@
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -15829,7 +15750,11 @@
           <t>مقيد ومنتظم</t>
         </is>
       </c>
-      <c r="J57" s="12" t="inlineStr"/>
+      <c r="J57" s="12" t="inlineStr">
+        <is>
+          <t>سجلات معتمدة 2026</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="12" t="n">
@@ -15837,12 +15762,12 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>SK-G2-LN-008</t>
+          <t>SK-G2-AR-005</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>مالك أحمد عبد المؤمن</t>
+          <t>مالك محمد الخشن</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -15857,7 +15782,7 @@
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">
@@ -15887,12 +15812,12 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>SK-G2-AR-005</t>
+          <t>SK-G2-LN-021</t>
         </is>
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>مالك محمد الخشن</t>
+          <t>محمد أحمد ضاحي</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -15907,7 +15832,7 @@
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -15937,12 +15862,12 @@
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>SK-G2-LN-021</t>
+          <t>SK-G2-LN-004</t>
         </is>
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>محمد أحمد ضاحي</t>
+          <t>معتز محمد عطاها</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
@@ -15987,12 +15912,12 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>SK-G2-LN-004</t>
+          <t>SK-G2-AR-001</t>
         </is>
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>معتز محمد عطاها</t>
+          <t>مهدي أحمد محمد</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -16007,7 +15932,7 @@
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -16037,12 +15962,12 @@
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>SK-G2-AR-001</t>
+          <t>SK-G2-LN-001</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>مهدي أحمد محمد</t>
+          <t>نوح عبد الحميد سمير</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -16057,7 +15982,7 @@
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G62" s="12" t="inlineStr">
@@ -16087,12 +16012,12 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>SK-G2-LN-001</t>
+          <t>SK-G2-LN-022</t>
         </is>
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>نوح عبد الحميد سمير</t>
+          <t>يزن حسام عطية</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -16137,12 +16062,12 @@
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>SK-G2-LN-022</t>
+          <t>SK-G3-LN-008</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>يزن حسام عطية</t>
+          <t>آدم خالد عبد الله</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -16152,7 +16077,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>الصف 2</t>
+          <t>الصف 3</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -16187,12 +16112,12 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-008</t>
+          <t>SK-G3-LN-006</t>
         </is>
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>آدم خالد عبد الله</t>
+          <t>آدم محمد صبحي</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -16237,12 +16162,12 @@
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-006</t>
+          <t>SK-G3-LN-002</t>
         </is>
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>آدم محمد صبحي</t>
+          <t>آسية أحمد مصطفى</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -16287,12 +16212,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-002</t>
+          <t>SK-G3-LN-009</t>
         </is>
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>آسية أحمد مصطفى</t>
+          <t>أدهم مصطفى وحيد</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -16337,12 +16262,12 @@
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-009</t>
+          <t>SK-G3-LN-003</t>
         </is>
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>أدهم مصطفى وحيد</t>
+          <t>أريام أحمد حسن</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -16387,12 +16312,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-003</t>
+          <t>SK-G3-AR-002</t>
         </is>
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>أريام أحمد حسن</t>
+          <t>أرين أشرف مجدى</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -16407,7 +16332,7 @@
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
@@ -16437,12 +16362,12 @@
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-AR-002</t>
+          <t>SK-G3-LN-015</t>
         </is>
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>أرين أشرف مجدى</t>
+          <t>أمين السيد أحمد</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -16457,7 +16382,7 @@
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
@@ -16487,12 +16412,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-015</t>
+          <t>SK-G3-AR-003</t>
         </is>
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>أمين السيد أحمد</t>
+          <t>الفاتح عبد القادر محمد</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -16507,7 +16432,7 @@
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
@@ -16537,12 +16462,12 @@
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-AR-003</t>
+          <t>SK-G3-LN-022</t>
         </is>
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>الفاتح عبد القادر محمد</t>
+          <t>تالين أحمد محمود</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -16557,7 +16482,7 @@
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G72" s="12" t="inlineStr">
@@ -16587,12 +16512,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-022</t>
+          <t>SK-G3-LN-014</t>
         </is>
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>تالين أحمد محمود</t>
+          <t>رائد عبد الكريم بشير</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -16637,12 +16562,12 @@
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-014</t>
+          <t>SK-G3-LN-021</t>
         </is>
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>رائد عبد الكريم بشير</t>
+          <t>ريتال محمد عسل</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -16687,12 +16612,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-021</t>
+          <t>SK-G3-LN-017</t>
         </is>
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>ريتال محمد عسل</t>
+          <t>ريمان جمال الحسين</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -16737,12 +16662,12 @@
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-017</t>
+          <t>SK-G3-LN-007</t>
         </is>
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>ريمان جمال الحسين</t>
+          <t>زين سليمان محمد</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -16787,12 +16712,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-007</t>
+          <t>SK-G3-LN-013</t>
         </is>
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>زين سليمان محمد</t>
+          <t>زين محمد نبيل نوار</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -16837,12 +16762,12 @@
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-013</t>
+          <t>SK-G3-LN-012</t>
         </is>
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>زين محمد نبيل نوار</t>
+          <t>شهم محمد أنور حرب</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -16887,12 +16812,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-012</t>
+          <t>SK-G3-LN-011</t>
         </is>
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>شهم محمد أنور حرب</t>
+          <t>عبد الرحمن خالد رجب</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -16937,12 +16862,12 @@
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-011</t>
+          <t>SK-G3-AR-005</t>
         </is>
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>عبد الرحمن خالد رجب</t>
+          <t>عبد الرحمن طه حسين</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -16957,7 +16882,7 @@
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G80" s="12" t="inlineStr">
@@ -16987,12 +16912,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-AR-005</t>
+          <t>SK-G3-AR-004</t>
         </is>
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>عبد الرحمن طه حسين</t>
+          <t>عمر محمود عبد الوهاب</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -17037,12 +16962,12 @@
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-AR-004</t>
+          <t>SK-G3-AR-3636</t>
         </is>
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>عمر محمود عبد الوهاب</t>
+          <t>فريدة محمد النجار</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -17075,11 +17000,7 @@
           <t>مقيد ومنتظم</t>
         </is>
       </c>
-      <c r="J82" s="12" t="inlineStr">
-        <is>
-          <t>سجلات معتمدة 2026</t>
-        </is>
-      </c>
+      <c r="J82" s="12" t="inlineStr"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="12" t="n">
@@ -17087,12 +17008,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-AR-3636</t>
+          <t>SK-G3-LN-004</t>
         </is>
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>فريدة محمد النجار</t>
+          <t>ليان سامح بسيوني</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -17107,7 +17028,7 @@
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -17125,7 +17046,11 @@
           <t>مقيد ومنتظم</t>
         </is>
       </c>
-      <c r="J83" s="12" t="inlineStr"/>
+      <c r="J83" s="12" t="inlineStr">
+        <is>
+          <t>سجلات معتمدة 2026</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="12" t="n">
@@ -17133,12 +17058,12 @@
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-004</t>
+          <t>SK-G3-LN-001</t>
         </is>
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>ليان سامح بسيوني</t>
+          <t>لين محمد عبد الحليم</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
@@ -17183,12 +17108,12 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-001</t>
+          <t>SK-G3-LN-020</t>
         </is>
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>لين محمد عبد الحليم</t>
+          <t>مؤيد أحمد سيد</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -17233,12 +17158,12 @@
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-020</t>
+          <t>SK-G3-LN-005</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>مؤيد أحمد سيد</t>
+          <t>ماريا خالد فهمي</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -17283,12 +17208,12 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-005</t>
+          <t>SK-G3-LN-019</t>
         </is>
       </c>
       <c r="C87" s="18" t="inlineStr">
         <is>
-          <t>ماريا خالد فهمي</t>
+          <t>مالك محمود ابراهيم</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -17333,12 +17258,12 @@
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-019</t>
+          <t>SK-G3-LN-018</t>
         </is>
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>مالك محمود ابراهيم</t>
+          <t>مصطفى عبد السلام مصطفى</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -17383,12 +17308,12 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-018</t>
+          <t>SK-G3-AR-001</t>
         </is>
       </c>
       <c r="C89" s="18" t="inlineStr">
         <is>
-          <t>مصطفى عبد السلام مصطفى</t>
+          <t>مليكة محمد عادل</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -17403,7 +17328,7 @@
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -17433,12 +17358,12 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-AR-001</t>
+          <t>SK-G3-LN-016</t>
         </is>
       </c>
       <c r="C90" s="18" t="inlineStr">
         <is>
-          <t>مليكة محمد عادل</t>
+          <t>نور أحمد عصام</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -17453,7 +17378,7 @@
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G90" s="12" t="inlineStr">
@@ -17483,12 +17408,12 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-016</t>
+          <t>SK-G3-AR-006</t>
         </is>
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>نور أحمد عصام</t>
+          <t>نور حماده عياد</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -17503,7 +17428,7 @@
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -17533,12 +17458,12 @@
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-AR-006</t>
+          <t>SK-G3-LN-010</t>
         </is>
       </c>
       <c r="C92" s="18" t="inlineStr">
         <is>
-          <t>نور حماده عياد</t>
+          <t>يوسف محمد عبد اللطيف</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -17553,7 +17478,7 @@
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G92" s="12" t="inlineStr">
@@ -17583,12 +17508,12 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>SK-G3-LN-010</t>
+          <t>SK-G4-LN-003</t>
         </is>
       </c>
       <c r="C93" s="18" t="inlineStr">
         <is>
-          <t>يوسف محمد عبد اللطيف</t>
+          <t>آدم عمرو أسامة</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -17598,7 +17523,7 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>الصف 3</t>
+          <t>الصف 4</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
@@ -17633,12 +17558,12 @@
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-003</t>
+          <t>SK-G4-AR-003</t>
         </is>
       </c>
       <c r="C94" s="18" t="inlineStr">
         <is>
-          <t>آدم عمرو أسامة</t>
+          <t>جانتي السيد عبد الغني</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -17683,12 +17608,12 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-AR-003</t>
+          <t>SK-G4-LN-013</t>
         </is>
       </c>
       <c r="C95" s="18" t="inlineStr">
         <is>
-          <t>جانتي السيد عبد الغني</t>
+          <t>جنة عمرو أبو المكارم</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -17733,12 +17658,12 @@
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-013</t>
+          <t>SK-G4-LN-001</t>
         </is>
       </c>
       <c r="C96" s="18" t="inlineStr">
         <is>
-          <t>جنة عمرو أبو المكارم</t>
+          <t>حمزة أحمد عبد الحميد</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -17783,12 +17708,12 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-001</t>
+          <t>SK-G4-LN-008</t>
         </is>
       </c>
       <c r="C97" s="18" t="inlineStr">
         <is>
-          <t>حمزة أحمد عبد الحميد</t>
+          <t>دانة السيد علي</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
@@ -17833,12 +17758,12 @@
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-008</t>
+          <t>SK-G4-LN-007</t>
         </is>
       </c>
       <c r="C98" s="18" t="inlineStr">
         <is>
-          <t>دانة السيد علي</t>
+          <t>ريان عبد الرحمن</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -17883,12 +17808,12 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-007</t>
+          <t>SK-G4-AR-006</t>
         </is>
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>ريان عبد الرحمن</t>
+          <t>عبد الله مروان الشيخ</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
@@ -17903,7 +17828,7 @@
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -17933,12 +17858,12 @@
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-AR-006</t>
+          <t>SK-G4-AR-004</t>
         </is>
       </c>
       <c r="C100" s="18" t="inlineStr">
         <is>
-          <t>عبد الله مروان الشيخ</t>
+          <t>على شريف على</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
@@ -17983,12 +17908,12 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-AR-004</t>
+          <t>SK-G4-LN-005</t>
         </is>
       </c>
       <c r="C101" s="18" t="inlineStr">
         <is>
-          <t>على شريف على</t>
+          <t>عمر أحمد الجزيرى</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
@@ -18003,7 +17928,7 @@
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -18033,12 +17958,12 @@
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-005</t>
+          <t>SK-G4-LN-011</t>
         </is>
       </c>
       <c r="C102" s="18" t="inlineStr">
         <is>
-          <t>عمر أحمد الجزيرى</t>
+          <t>فيروز هشام محمد</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -18083,12 +18008,12 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-011</t>
+          <t>SK-G4-AR-002</t>
         </is>
       </c>
       <c r="C103" s="18" t="inlineStr">
         <is>
-          <t>فيروز هشام محمد</t>
+          <t>كارما أحمد عطية</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
@@ -18103,7 +18028,7 @@
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -18133,12 +18058,12 @@
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-AR-002</t>
+          <t>SK-G4-LN-009</t>
         </is>
       </c>
       <c r="C104" s="18" t="inlineStr">
         <is>
-          <t>كارما أحمد عطية</t>
+          <t>كارما محمد حسام</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -18153,7 +18078,7 @@
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G104" s="12" t="inlineStr">
@@ -18183,12 +18108,12 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-009</t>
+          <t>SK-G4-LN-012</t>
         </is>
       </c>
       <c r="C105" s="18" t="inlineStr">
         <is>
-          <t>كارما محمد حسام</t>
+          <t>لوجين وليد محمد</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -18233,12 +18158,12 @@
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-012</t>
+          <t>SK-G4-AR-005</t>
         </is>
       </c>
       <c r="C106" s="18" t="inlineStr">
         <is>
-          <t>لوجين وليد محمد</t>
+          <t>محمد محمود الصياد</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -18253,7 +18178,7 @@
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G106" s="12" t="inlineStr">
@@ -18283,12 +18208,12 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-AR-005</t>
+          <t>SK-G4-AR-001</t>
         </is>
       </c>
       <c r="C107" s="18" t="inlineStr">
         <is>
-          <t>محمد محمود الصياد</t>
+          <t>مها رضوان تسون</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
@@ -18333,12 +18258,12 @@
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-AR-001</t>
+          <t>SK-G4-LN-002</t>
         </is>
       </c>
       <c r="C108" s="18" t="inlineStr">
         <is>
-          <t>مها رضوان تسون</t>
+          <t>مهيب جمال فتح الله</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -18353,7 +18278,7 @@
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G108" s="12" t="inlineStr">
@@ -18383,12 +18308,12 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-002</t>
+          <t>SK-G4-LN-010</t>
         </is>
       </c>
       <c r="C109" s="18" t="inlineStr">
         <is>
-          <t>مهيب جمال فتح الله</t>
+          <t>ميرا محمد عطاها</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
@@ -18433,12 +18358,12 @@
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-010</t>
+          <t>SK-G4-LN-006</t>
         </is>
       </c>
       <c r="C110" s="18" t="inlineStr">
         <is>
-          <t>ميرا محمد عطاها</t>
+          <t>يحيي محمد فاروق</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
@@ -18483,12 +18408,12 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-006</t>
+          <t>SK-G4-LN-004</t>
         </is>
       </c>
       <c r="C111" s="18" t="inlineStr">
         <is>
-          <t>يحيي محمد فاروق</t>
+          <t>يوسف كمال محمد</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
@@ -18533,12 +18458,12 @@
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-004</t>
+          <t>SK-G5-LN-005</t>
         </is>
       </c>
       <c r="C112" s="18" t="inlineStr">
         <is>
-          <t>يوسف كمال محمد</t>
+          <t>أيسل محمد السعيد</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
@@ -18548,7 +18473,7 @@
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>الصف 4</t>
+          <t>الصف 5</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
@@ -18583,12 +18508,12 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-005</t>
+          <t>SK-G5-AR-003</t>
         </is>
       </c>
       <c r="C113" s="18" t="inlineStr">
         <is>
-          <t>أيسل محمد السعيد</t>
+          <t>جودى مهند خضرو</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
@@ -18603,7 +18528,7 @@
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -18633,12 +18558,12 @@
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-003</t>
+          <t>SK-G5-AR-002</t>
         </is>
       </c>
       <c r="C114" s="18" t="inlineStr">
         <is>
-          <t>جودى مهند خضرو</t>
+          <t>جويرية أحمد عطيه</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
@@ -18683,12 +18608,12 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-002</t>
+          <t>SK-G5-AR-006</t>
         </is>
       </c>
       <c r="C115" s="18" t="inlineStr">
         <is>
-          <t>جويرية أحمد عطيه</t>
+          <t>رفيدة خالد رجب</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
@@ -18733,12 +18658,12 @@
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-006</t>
+          <t>SK-G5-LN-004</t>
         </is>
       </c>
       <c r="C116" s="18" t="inlineStr">
         <is>
-          <t>رفيدة خالد رجب</t>
+          <t>رقية رضا عبد المقصود</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
@@ -18753,7 +18678,7 @@
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
@@ -18783,12 +18708,12 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-004</t>
+          <t>SK-G5-LN-003</t>
         </is>
       </c>
       <c r="C117" s="18" t="inlineStr">
         <is>
-          <t>رقية رضا عبد المقصود</t>
+          <t>رودينة عبد الله السيد</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
@@ -18833,12 +18758,12 @@
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-003</t>
+          <t>SK-G5-AR-007</t>
         </is>
       </c>
       <c r="C118" s="18" t="inlineStr">
         <is>
-          <t>رودينة عبد الله السيد</t>
+          <t>زياد مصطفى فرج</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
@@ -18853,7 +18778,7 @@
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G118" s="12" t="inlineStr">
@@ -18883,12 +18808,12 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-007</t>
+          <t>SK-G5-AR-009</t>
         </is>
       </c>
       <c r="C119" s="18" t="inlineStr">
         <is>
-          <t>زياد مصطفى فرج</t>
+          <t>سامح طه النقاش</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
@@ -18933,12 +18858,12 @@
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-009</t>
+          <t>SK-G5-LN-002</t>
         </is>
       </c>
       <c r="C120" s="18" t="inlineStr">
         <is>
-          <t>سامح طه النقاش</t>
+          <t>عائشة محمد علاء الدين</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
@@ -18953,7 +18878,7 @@
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G120" s="12" t="inlineStr">
@@ -18983,12 +18908,12 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-002</t>
+          <t>SK-G5-AR-008</t>
         </is>
       </c>
       <c r="C121" s="18" t="inlineStr">
         <is>
-          <t>عائشة محمد علاء الدين</t>
+          <t>عبد الله محمود الصياد</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
@@ -19003,7 +18928,7 @@
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
@@ -19033,12 +18958,12 @@
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-008</t>
+          <t>SK-G5-AR-001</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>عبد الله محمود الصياد</t>
+          <t>كيان محمود منصور</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
@@ -19083,12 +19008,12 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-001</t>
+          <t>SK-G5-LN-001</t>
         </is>
       </c>
       <c r="C123" s="18" t="inlineStr">
         <is>
-          <t>كيان محمود منصور</t>
+          <t>لينا أحمد شوقى</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
@@ -19103,7 +19028,7 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G123" s="12" t="inlineStr">
@@ -19133,12 +19058,12 @@
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-001</t>
+          <t>SK-G5-AR-005</t>
         </is>
       </c>
       <c r="C124" s="18" t="inlineStr">
         <is>
-          <t>لينا أحمد شوقى</t>
+          <t>ليندا هشام أحمد</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
@@ -19153,7 +19078,7 @@
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G124" s="12" t="inlineStr">
@@ -19183,12 +19108,12 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-005</t>
+          <t>SK-G5-LN-009</t>
         </is>
       </c>
       <c r="C125" s="18" t="inlineStr">
         <is>
-          <t>ليندا هشام أحمد</t>
+          <t>محمد أدهم حربي</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
@@ -19203,7 +19128,7 @@
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G125" s="12" t="inlineStr">
@@ -19233,12 +19158,12 @@
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-009</t>
+          <t>SK-G5-LN-008</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
         <is>
-          <t>محمد أدهم حربي</t>
+          <t>محمد عمرو محمد</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
@@ -19283,12 +19208,12 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-008</t>
+          <t>SK-G5-LN-007</t>
         </is>
       </c>
       <c r="C127" s="18" t="inlineStr">
         <is>
-          <t>محمد عمرو محمد</t>
+          <t>مريم حمدى أحمد</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
@@ -19333,12 +19258,12 @@
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-007</t>
+          <t>SK-G5-AR-010</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>مريم حمدى أحمد</t>
+          <t>مصطفى أحمد مصطفى</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
@@ -19353,7 +19278,7 @@
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G128" s="12" t="inlineStr">
@@ -19383,12 +19308,12 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-010</t>
+          <t>SK-G5-AR-004</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>مصطفى أحمد مصطفى</t>
+          <t>ملك محمد</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
@@ -19433,12 +19358,12 @@
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-004</t>
+          <t>SK-G5-LN-006</t>
         </is>
       </c>
       <c r="C130" s="18" t="inlineStr">
         <is>
-          <t>ملك محمد</t>
+          <t>مليكة محمد نوار</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
@@ -19453,7 +19378,7 @@
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G130" s="12" t="inlineStr">
@@ -19483,12 +19408,12 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-006</t>
+          <t>SK-G6-LN-005</t>
         </is>
       </c>
       <c r="C131" s="18" t="inlineStr">
         <is>
-          <t>مليكة محمد نوار</t>
+          <t>أروى محمد أحمد</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
@@ -19498,7 +19423,7 @@
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>الصف 5</t>
+          <t>الصف 6</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
@@ -19533,12 +19458,12 @@
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-005</t>
+          <t>SK-G6-AR-004</t>
         </is>
       </c>
       <c r="C132" s="18" t="inlineStr">
         <is>
-          <t>أروى محمد أحمد</t>
+          <t>أسيل حمد أحمد</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
@@ -19553,7 +19478,7 @@
       </c>
       <c r="F132" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G132" s="12" t="inlineStr">
@@ -19583,12 +19508,12 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-AR-004</t>
+          <t>SK-G6-LN-011</t>
         </is>
       </c>
       <c r="C133" s="18" t="inlineStr">
         <is>
-          <t>أسيل حمد أحمد</t>
+          <t>أفنان أحمد</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
@@ -19603,7 +19528,7 @@
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
@@ -19633,12 +19558,12 @@
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-011</t>
+          <t>SK-G6-AR-003</t>
         </is>
       </c>
       <c r="C134" s="18" t="inlineStr">
         <is>
-          <t>أفنان أحمد</t>
+          <t>باسم حسن العمري</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
@@ -19653,7 +19578,7 @@
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G134" s="12" t="inlineStr">
@@ -19683,12 +19608,12 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-AR-003</t>
+          <t>SK-G6-LN-002</t>
         </is>
       </c>
       <c r="C135" s="18" t="inlineStr">
         <is>
-          <t>باسم حسن العمري</t>
+          <t>سيف جمال إسماعيل</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
@@ -19703,7 +19628,7 @@
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
@@ -19733,12 +19658,12 @@
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-002</t>
+          <t>SK-G6-LN-010</t>
         </is>
       </c>
       <c r="C136" s="18" t="inlineStr">
         <is>
-          <t>سيف جمال إسماعيل</t>
+          <t>لارين أحمد الشوني</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
@@ -19783,12 +19708,12 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-010</t>
+          <t>SK-G6-LN-009</t>
         </is>
       </c>
       <c r="C137" s="18" t="inlineStr">
         <is>
-          <t>لارين أحمد الشوني</t>
+          <t>لورين وليد محمد</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
@@ -19833,12 +19758,12 @@
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-009</t>
+          <t>SK-G6-LN-008</t>
         </is>
       </c>
       <c r="C138" s="18" t="inlineStr">
         <is>
-          <t>لورين وليد محمد</t>
+          <t>ليان السيد على</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
@@ -19883,12 +19808,12 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-008</t>
+          <t>SK-G6-LN-006</t>
         </is>
       </c>
       <c r="C139" s="18" t="inlineStr">
         <is>
-          <t>ليان السيد على</t>
+          <t>ليليا مازن شلار</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
@@ -19933,12 +19858,12 @@
       </c>
       <c r="B140" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-006</t>
+          <t>SK-G6-AR-002</t>
         </is>
       </c>
       <c r="C140" s="18" t="inlineStr">
         <is>
-          <t>ليليا مازن شلار</t>
+          <t>لينا هشام أحمد</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
@@ -19953,7 +19878,7 @@
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G140" s="12" t="inlineStr">
@@ -19983,12 +19908,12 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-AR-002</t>
+          <t>SK-G6-LN-007</t>
         </is>
       </c>
       <c r="C141" s="18" t="inlineStr">
         <is>
-          <t>لينا هشام أحمد</t>
+          <t>ماسة محمد أنور</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
@@ -20003,7 +19928,7 @@
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
@@ -20033,12 +19958,12 @@
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-007</t>
+          <t>SK-G6-LN-003</t>
         </is>
       </c>
       <c r="C142" s="18" t="inlineStr">
         <is>
-          <t>ماسة محمد أنور</t>
+          <t>مالك محمود عبد الحميد</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
@@ -20083,12 +20008,12 @@
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-003</t>
+          <t>SK-G6-LN-001</t>
         </is>
       </c>
       <c r="C143" s="18" t="inlineStr">
         <is>
-          <t>مالك محمود عبد الحميد</t>
+          <t>محمد السيد سمير</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
@@ -20133,12 +20058,12 @@
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-001</t>
+          <t>SK-G6-LN-004</t>
         </is>
       </c>
       <c r="C144" s="18" t="inlineStr">
         <is>
-          <t>محمد السيد سمير</t>
+          <t>محمد مصطفى وحيد</t>
         </is>
       </c>
       <c r="D144" s="12" t="inlineStr">
@@ -20183,12 +20108,12 @@
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-004</t>
+          <t>SK-G6-AR-005</t>
         </is>
       </c>
       <c r="C145" s="18" t="inlineStr">
         <is>
-          <t>محمد مصطفى وحيد</t>
+          <t>هدى محمد مجدى</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
@@ -20203,7 +20128,7 @@
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G145" s="12" t="inlineStr">
@@ -20233,12 +20158,12 @@
       </c>
       <c r="B146" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-AR-005</t>
+          <t>SK-G6-AR-001</t>
         </is>
       </c>
       <c r="C146" s="18" t="inlineStr">
         <is>
-          <t>هدى محمد مجدى</t>
+          <t>ياسين إسلام حمد</t>
         </is>
       </c>
       <c r="D146" s="12" t="inlineStr">
@@ -20283,12 +20208,12 @@
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-AR-001</t>
+          <t>SK-G7-LN-008</t>
         </is>
       </c>
       <c r="C147" s="18" t="inlineStr">
         <is>
-          <t>ياسين إسلام حمد</t>
+          <t>آدم عبد الحميد عيد</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
@@ -20298,12 +20223,12 @@
       </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>الصف 6</t>
+          <t>الصف 7</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G147" s="12" t="inlineStr">
@@ -20333,12 +20258,12 @@
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-008</t>
+          <t>SK-G7-AR-006</t>
         </is>
       </c>
       <c r="C148" s="18" t="inlineStr">
         <is>
-          <t>آدم عبد الحميد عيد</t>
+          <t>بلال محمد عادل</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
@@ -20353,7 +20278,7 @@
       </c>
       <c r="F148" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G148" s="12" t="inlineStr">
@@ -20383,12 +20308,12 @@
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-AR-006</t>
+          <t>SK-G7-LN-003</t>
         </is>
       </c>
       <c r="C149" s="18" t="inlineStr">
         <is>
-          <t>بلال محمد عادل</t>
+          <t>تقى أحمد محمود</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
@@ -20403,7 +20328,7 @@
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
@@ -20433,12 +20358,12 @@
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-003</t>
+          <t>SK-G7-LN-004</t>
         </is>
       </c>
       <c r="C150" s="18" t="inlineStr">
         <is>
-          <t>تقى أحمد محمود</t>
+          <t>جودى خالد رجب</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
@@ -20483,12 +20408,12 @@
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-004</t>
+          <t>SK-G7-AR-004</t>
         </is>
       </c>
       <c r="C151" s="18" t="inlineStr">
         <is>
-          <t>جودى خالد رجب</t>
+          <t>سارة أحمد مصطفى</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
@@ -20503,7 +20428,7 @@
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G151" s="12" t="inlineStr">
@@ -20533,12 +20458,12 @@
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-AR-004</t>
+          <t>SK-G7-AR-005</t>
         </is>
       </c>
       <c r="C152" s="18" t="inlineStr">
         <is>
-          <t>سارة أحمد مصطفى</t>
+          <t>عمار محمود سعد</t>
         </is>
       </c>
       <c r="D152" s="12" t="inlineStr">
@@ -20583,12 +20508,12 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-AR-005</t>
+          <t>SK-G7-LN-007</t>
         </is>
       </c>
       <c r="C153" s="18" t="inlineStr">
         <is>
-          <t>عمار محمود سعد</t>
+          <t>عمر أحمد عصام</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
@@ -20603,7 +20528,7 @@
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
@@ -20633,12 +20558,12 @@
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-007</t>
+          <t>SK-G7-AR-003</t>
         </is>
       </c>
       <c r="C154" s="18" t="inlineStr">
         <is>
-          <t>عمر أحمد عصام</t>
+          <t>فريدة شريف رجب</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
@@ -20653,7 +20578,7 @@
       </c>
       <c r="F154" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G154" s="12" t="inlineStr">
@@ -20683,12 +20608,12 @@
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-AR-003</t>
+          <t>SK-G7-AR-002</t>
         </is>
       </c>
       <c r="C155" s="18" t="inlineStr">
         <is>
-          <t>فريدة شريف رجب</t>
+          <t>ليان محمود رزق</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
@@ -20733,12 +20658,12 @@
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-AR-002</t>
+          <t>SK-G7-LN-006</t>
         </is>
       </c>
       <c r="C156" s="18" t="inlineStr">
         <is>
-          <t>ليان محمود رزق</t>
+          <t>مالك أدهم حربي</t>
         </is>
       </c>
       <c r="D156" s="12" t="inlineStr">
@@ -20753,7 +20678,7 @@
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G156" s="12" t="inlineStr">
@@ -20783,12 +20708,12 @@
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-006</t>
+          <t>SK-G7-LN-001</t>
         </is>
       </c>
       <c r="C157" s="18" t="inlineStr">
         <is>
-          <t>مالك أدهم حربي</t>
+          <t>مايا هيثم رشوان</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
@@ -20833,12 +20758,12 @@
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-001</t>
+          <t>SK-G7-LN-002</t>
         </is>
       </c>
       <c r="C158" s="18" t="inlineStr">
         <is>
-          <t>مايا هيثم رشوان</t>
+          <t>مريم أدهم حربي</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
@@ -20883,12 +20808,12 @@
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-002</t>
+          <t>SK-G7-AR-001</t>
         </is>
       </c>
       <c r="C159" s="18" t="inlineStr">
         <is>
-          <t>مريم أدهم حربي</t>
+          <t>نورسان إسلام محمد</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
@@ -20903,7 +20828,7 @@
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G159" s="12" t="inlineStr">
@@ -20933,12 +20858,12 @@
       </c>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-AR-001</t>
+          <t>SK-G7-LN-005</t>
         </is>
       </c>
       <c r="C160" s="18" t="inlineStr">
         <is>
-          <t>نورسان إسلام محمد</t>
+          <t>ياسين سليمان محمد</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
@@ -20953,7 +20878,7 @@
       </c>
       <c r="F160" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G160" s="12" t="inlineStr">
@@ -20983,12 +20908,12 @@
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-005</t>
+          <t>SK-G8-LN-001</t>
         </is>
       </c>
       <c r="C161" s="18" t="inlineStr">
         <is>
-          <t>ياسين سليمان محمد</t>
+          <t>بسملة عبد الله سيد</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
@@ -20998,7 +20923,7 @@
       </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>الصف 7</t>
+          <t>الصف 8</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
@@ -21033,12 +20958,12 @@
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t>SK-G8-LN-001</t>
+          <t>SK-G8-AR-002</t>
         </is>
       </c>
       <c r="C162" s="18" t="inlineStr">
         <is>
-          <t>بسملة عبد الله سيد</t>
+          <t>سجد محمود منصور</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
@@ -21053,7 +20978,7 @@
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G162" s="12" t="inlineStr">
@@ -21083,12 +21008,12 @@
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>SK-G8-AR-002</t>
+          <t>SK-G8-AR-003</t>
         </is>
       </c>
       <c r="C163" s="18" t="inlineStr">
         <is>
-          <t>سجد محمود منصور</t>
+          <t>عبد الغني عصام عبد الله</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
@@ -21133,12 +21058,12 @@
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t>SK-G8-AR-003</t>
+          <t>SK-G8-AR-001</t>
         </is>
       </c>
       <c r="C164" s="18" t="inlineStr">
         <is>
-          <t>عبد الغني عصام عبد الله</t>
+          <t>محمد حسن العمري</t>
         </is>
       </c>
       <c r="D164" s="12" t="inlineStr">
@@ -21183,12 +21108,12 @@
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>SK-G8-AR-001</t>
+          <t>SK-G8-LN-002</t>
         </is>
       </c>
       <c r="C165" s="18" t="inlineStr">
         <is>
-          <t>محمد حسن العمري</t>
+          <t>وتين أحمد الشوني</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
@@ -21203,7 +21128,7 @@
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G165" s="12" t="inlineStr">
@@ -21233,12 +21158,12 @@
       </c>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t>SK-G8-LN-002</t>
+          <t>SK-G9-LN-001</t>
         </is>
       </c>
       <c r="C166" s="18" t="inlineStr">
         <is>
-          <t>وتين أحمد الشوني</t>
+          <t>أحمد رضا شوشة</t>
         </is>
       </c>
       <c r="D166" s="12" t="inlineStr">
@@ -21248,7 +21173,7 @@
       </c>
       <c r="E166" s="12" t="inlineStr">
         <is>
-          <t>الصف 8</t>
+          <t>الصف 9</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
@@ -21283,12 +21208,12 @@
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>SK-G9-LN-001</t>
+          <t>SK-G9-AR-002</t>
         </is>
       </c>
       <c r="C167" s="18" t="inlineStr">
         <is>
-          <t>أحمد رضا شوشة</t>
+          <t>أيمن عصام القاضي</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
@@ -21303,7 +21228,7 @@
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G167" s="12" t="inlineStr">
@@ -21333,12 +21258,12 @@
       </c>
       <c r="B168" s="12" t="inlineStr">
         <is>
-          <t>SK-G9-AR-002</t>
+          <t>SK-G9-LN-002</t>
         </is>
       </c>
       <c r="C168" s="18" t="inlineStr">
         <is>
-          <t>أيمن عصام القاضي</t>
+          <t>جودى هيثم رشوان</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
@@ -21353,7 +21278,7 @@
       </c>
       <c r="F168" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G168" s="12" t="inlineStr">
@@ -21383,12 +21308,12 @@
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>SK-G9-LN-002</t>
+          <t>SK-G9-AR-001</t>
         </is>
       </c>
       <c r="C169" s="18" t="inlineStr">
         <is>
-          <t>جودى هيثم رشوان</t>
+          <t>ساره محمد عطاها</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
@@ -21403,7 +21328,7 @@
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G169" s="12" t="inlineStr">
@@ -21433,12 +21358,12 @@
       </c>
       <c r="B170" s="12" t="inlineStr">
         <is>
-          <t>SK-G9-AR-001</t>
+          <t>SK-G9-AR-003</t>
         </is>
       </c>
       <c r="C170" s="18" t="inlineStr">
         <is>
-          <t>ساره محمد عطاها</t>
+          <t>محمد عبد الله النقاش</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
@@ -21472,56 +21397,6 @@
         </is>
       </c>
       <c r="J170" s="12" t="inlineStr">
-        <is>
-          <t>سجلات معتمدة 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="18" customHeight="1">
-      <c r="A171" s="12" t="n">
-        <v>170</v>
-      </c>
-      <c r="B171" s="12" t="inlineStr">
-        <is>
-          <t>SK-G9-AR-003</t>
-        </is>
-      </c>
-      <c r="C171" s="18" t="inlineStr">
-        <is>
-          <t>محمد عبد الله النقاش</t>
-        </is>
-      </c>
-      <c r="D171" s="12" t="inlineStr">
-        <is>
-          <t>29801011234567</t>
-        </is>
-      </c>
-      <c r="E171" s="12" t="inlineStr">
-        <is>
-          <t>الصف 9</t>
-        </is>
-      </c>
-      <c r="F171" s="12" t="inlineStr">
-        <is>
-          <t>عربي</t>
-        </is>
-      </c>
-      <c r="G171" s="12" t="inlineStr">
-        <is>
-          <t>مسلم</t>
-        </is>
-      </c>
-      <c r="H171" s="12" t="inlineStr">
-        <is>
-          <t>01000000000</t>
-        </is>
-      </c>
-      <c r="I171" s="12" t="inlineStr">
-        <is>
-          <t>مقيد ومنتظم</t>
-        </is>
-      </c>
-      <c r="J171" s="12" t="inlineStr">
         <is>
           <t>سجلات معتمدة 2026</t>
         </is>

--- a/Smile_Kids_Grades_Master_Backup.xlsx
+++ b/Smile_Kids_Grades_Master_Backup.xlsx
@@ -568,8 +568,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q173"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:Q178"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -600,7 +600,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>إجمالي الطلاب: 169 طالب • العام الدراسي 2026/2027 • موحد مع بوابات المعلمات والكنترول الإداري</t>
+          <t>إجمالي الطلاب: 174 طالب • العام الدراسي 2026/2027 • موحد مع بوابات المعلمات والكنترول الإداري</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
         <v>19.5</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="N6" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O6" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P6" s="16" t="inlineStr">
@@ -880,7 +880,7 @@
         <v>19.5</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -898,11 +898,11 @@
         </is>
       </c>
       <c r="N7" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P7" s="16" t="inlineStr">
@@ -1027,10 +1027,10 @@
         <v>19.5</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="N9" s="16" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="P9" s="16" t="inlineStr">
@@ -1105,7 +1105,7 @@
         <v>19.5</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
         </is>
       </c>
       <c r="N10" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O10" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P10" s="16" t="inlineStr">
@@ -1180,7 +1180,7 @@
         <v>19.5</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
@@ -1198,11 +1198,11 @@
         </is>
       </c>
       <c r="N11" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P11" s="16" t="inlineStr">
@@ -1330,7 +1330,7 @@
         <v>19.5</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
@@ -1348,11 +1348,11 @@
         </is>
       </c>
       <c r="N13" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P13" s="16" t="inlineStr">
@@ -1405,7 +1405,7 @@
         <v>19.5</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
@@ -1423,11 +1423,11 @@
         </is>
       </c>
       <c r="N14" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O14" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P14" s="16" t="inlineStr">
@@ -1480,7 +1480,7 @@
         <v>19.5</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="N15" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O15" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P15" s="16" t="inlineStr">
@@ -1705,7 +1705,7 @@
         <v>20</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
@@ -1723,11 +1723,11 @@
         </is>
       </c>
       <c r="N18" s="16" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O18" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>112.5%</t>
         </is>
       </c>
       <c r="P18" s="16" t="inlineStr">
@@ -1780,7 +1780,7 @@
         <v>19.5</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
@@ -1798,11 +1798,11 @@
         </is>
       </c>
       <c r="N19" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O19" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P19" s="16" t="inlineStr">
@@ -1855,7 +1855,7 @@
         <v>19.5</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
@@ -1873,11 +1873,11 @@
         </is>
       </c>
       <c r="N20" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O20" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P20" s="16" t="inlineStr">
@@ -2005,7 +2005,7 @@
         <v>19.5</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
@@ -2023,11 +2023,11 @@
         </is>
       </c>
       <c r="N22" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O22" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P22" s="16" t="inlineStr">
@@ -2230,7 +2230,7 @@
         <v>19.5</v>
       </c>
       <c r="J25" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
@@ -2248,11 +2248,11 @@
         </is>
       </c>
       <c r="N25" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O25" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P25" s="16" t="inlineStr">
@@ -2455,7 +2455,7 @@
         <v>19.5</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
@@ -2473,11 +2473,11 @@
         </is>
       </c>
       <c r="N28" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O28" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P28" s="16" t="inlineStr">
@@ -2605,7 +2605,7 @@
         <v>19.5</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
@@ -2623,11 +2623,11 @@
         </is>
       </c>
       <c r="N30" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O30" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P30" s="16" t="inlineStr">
@@ -2680,7 +2680,7 @@
         <v>19.5</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
@@ -2698,11 +2698,11 @@
         </is>
       </c>
       <c r="N31" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O31" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P31" s="16" t="inlineStr">
@@ -2755,7 +2755,7 @@
         <v>19.5</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
@@ -2773,11 +2773,11 @@
         </is>
       </c>
       <c r="N32" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O32" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P32" s="16" t="inlineStr">
@@ -2830,7 +2830,7 @@
         <v>19.5</v>
       </c>
       <c r="J33" s="13" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
@@ -2848,11 +2848,11 @@
         </is>
       </c>
       <c r="N33" s="16" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="O33" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="P33" s="16" t="inlineStr">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="G34" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H34" s="13" t="n">
         <v>19.5</v>
@@ -2923,11 +2923,11 @@
         </is>
       </c>
       <c r="N34" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O34" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P34" s="16" t="inlineStr">
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="G36" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H36" s="13" t="n">
         <v>19.5</v>
@@ -3073,11 +3073,11 @@
         </is>
       </c>
       <c r="N36" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O36" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P36" s="16" t="inlineStr">
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="G37" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H37" s="13" t="n">
         <v>19.5</v>
@@ -3148,11 +3148,11 @@
         </is>
       </c>
       <c r="N37" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O37" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P37" s="16" t="inlineStr">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="G38" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H38" s="13" t="n">
         <v>19.5</v>
@@ -3223,11 +3223,11 @@
         </is>
       </c>
       <c r="N38" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O38" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P38" s="16" t="inlineStr">
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="G39" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H39" s="13" t="n">
         <v>19.5</v>
@@ -3298,11 +3298,11 @@
         </is>
       </c>
       <c r="N39" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O39" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P39" s="16" t="inlineStr">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="G41" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H41" s="13" t="n">
         <v>19.5</v>
@@ -3448,11 +3448,11 @@
         </is>
       </c>
       <c r="N41" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O41" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P41" s="16" t="inlineStr">
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="G42" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H42" s="13" t="n">
         <v>19.5</v>
@@ -3523,11 +3523,11 @@
         </is>
       </c>
       <c r="N42" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O42" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P42" s="16" t="inlineStr">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="G43" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H43" s="13" t="n">
         <v>19.5</v>
@@ -3598,11 +3598,11 @@
         </is>
       </c>
       <c r="N43" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O43" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P43" s="16" t="inlineStr">
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="G44" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H44" s="13" t="n">
         <v>19.5</v>
@@ -3673,11 +3673,11 @@
         </is>
       </c>
       <c r="N44" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O44" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P44" s="16" t="inlineStr">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G47" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H47" s="13" t="n">
         <v>19.5</v>
@@ -3898,11 +3898,11 @@
         </is>
       </c>
       <c r="N47" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O47" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P47" s="16" t="inlineStr">
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="G48" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H48" s="13" t="n">
         <v>19.5</v>
@@ -3973,11 +3973,11 @@
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O48" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P48" s="16" t="inlineStr">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G49" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H49" s="13" t="n">
         <v>19.5</v>
@@ -4048,11 +4048,11 @@
         </is>
       </c>
       <c r="N49" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O49" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P49" s="16" t="inlineStr">
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="G50" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H50" s="13" t="n">
         <v>19.5</v>
@@ -4123,11 +4123,11 @@
         </is>
       </c>
       <c r="N50" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O50" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P50" s="16" t="inlineStr">
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="G51" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H51" s="13" t="n">
         <v>19.5</v>
@@ -4198,11 +4198,11 @@
         </is>
       </c>
       <c r="N51" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O51" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P51" s="16" t="inlineStr">
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="G52" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H52" s="13" t="n">
         <v>19.5</v>
@@ -4273,11 +4273,11 @@
         </is>
       </c>
       <c r="N52" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O52" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P52" s="16" t="inlineStr">
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="G54" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H54" s="13" t="n">
         <v>19.5</v>
@@ -4423,11 +4423,11 @@
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O54" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P54" s="16" t="inlineStr">
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="G56" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H56" s="13" t="n">
         <v>19.5</v>
@@ -4573,11 +4573,11 @@
         </is>
       </c>
       <c r="N56" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O56" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P56" s="16" t="inlineStr">
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="G57" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H57" s="13" t="n">
         <v>19.5</v>
@@ -4648,11 +4648,11 @@
         </is>
       </c>
       <c r="N57" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O57" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P57" s="16" t="inlineStr">
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="G59" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H59" s="13" t="n">
         <v>19.5</v>
@@ -4798,11 +4798,11 @@
         </is>
       </c>
       <c r="N59" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O59" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P59" s="16" t="inlineStr">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="G60" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H60" s="13" t="n">
         <v>19.5</v>
@@ -4873,11 +4873,11 @@
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O60" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P60" s="16" t="inlineStr">
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="G61" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H61" s="13" t="n">
         <v>19.5</v>
@@ -4948,11 +4948,11 @@
         </is>
       </c>
       <c r="N61" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O61" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P61" s="16" t="inlineStr">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="G63" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H63" s="13" t="n">
         <v>19.5</v>
@@ -5098,11 +5098,11 @@
         </is>
       </c>
       <c r="N63" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O63" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P63" s="16" t="inlineStr">
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="G64" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H64" s="13" t="n">
         <v>19.5</v>
@@ -5173,11 +5173,11 @@
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O64" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P64" s="16" t="inlineStr">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="G65" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H65" s="13" t="n">
         <v>19.5</v>
@@ -5248,11 +5248,11 @@
         </is>
       </c>
       <c r="N65" s="16" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="O65" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="P65" s="16" t="inlineStr">
@@ -7867,17 +7867,17 @@
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-007</t>
+          <t>SK-G4-EN-6103</t>
         </is>
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>ريان عبد الرحمن</t>
+          <t>روفان عمر عبد المقصود</t>
         </is>
       </c>
       <c r="D101" s="15" t="inlineStr">
         <is>
-          <t>Rayan Abdel Rahman</t>
+          <t>Rovan Omar Abdelmaksoud</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
@@ -7891,32 +7891,32 @@
         </is>
       </c>
       <c r="G101" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H101" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I101" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J101" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K101" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="L101" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M101" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="N101" s="16" t="n">
-        <v>136.5</v>
+        <v>140</v>
       </c>
       <c r="O101" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P101" s="16" t="inlineStr">
@@ -7936,17 +7936,17 @@
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-AR-006</t>
+          <t>SK-G4-LN-007</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>عبد الله مروان الشيخ</t>
+          <t>ريان عبد الرحمن</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>Abdullah Marwan El-Sheikh</t>
+          <t>Rayan Abdel Rahman</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G102" s="13" t="n">
@@ -8005,17 +8005,17 @@
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-AR-004</t>
+          <t>SK-G4-AR-006</t>
         </is>
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
-          <t>على شريف على</t>
+          <t>عبد الله مروان الشيخ</t>
         </is>
       </c>
       <c r="D103" s="15" t="inlineStr">
         <is>
-          <t>Ali Sherif Ali</t>
+          <t>Abdullah Marwan El-Sheikh</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
@@ -8074,17 +8074,17 @@
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-005</t>
+          <t>SK-G4-AR-004</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>عمر أحمد الجزيرى</t>
+          <t>على شريف على</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>Omar Ahmed El-Gezeiry</t>
+          <t>Ali Sherif Ali</t>
         </is>
       </c>
       <c r="E104" s="12" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G104" s="13" t="n">
@@ -8143,17 +8143,17 @@
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-011</t>
+          <t>SK-G4-LN-005</t>
         </is>
       </c>
       <c r="C105" s="14" t="inlineStr">
         <is>
-          <t>فيروز هشام محمد</t>
+          <t>عمر أحمد الجزيرى</t>
         </is>
       </c>
       <c r="D105" s="15" t="inlineStr">
         <is>
-          <t>Fayrouz Hesham Mohamed</t>
+          <t>Omar Ahmed El-Gezeiry</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
@@ -8212,17 +8212,17 @@
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-AR-002</t>
+          <t>SK-G4-LN-011</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>كارما أحمد عطية</t>
+          <t>فيروز هشام محمد</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>Karma Ahmed Attia</t>
+          <t>Fayrouz Hesham Mohamed</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G106" s="13" t="n">
@@ -8281,17 +8281,17 @@
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-009</t>
+          <t>SK-G4-AR-002</t>
         </is>
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>كارما محمد حسام</t>
+          <t>كارما أحمد عطية</t>
         </is>
       </c>
       <c r="D107" s="15" t="inlineStr">
         <is>
-          <t>Karma Mohamed Hossam</t>
+          <t>Karma Ahmed Attia</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G107" s="13" t="n">
@@ -8350,17 +8350,17 @@
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-012</t>
+          <t>SK-G4-LN-009</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>لوجين وليد محمد</t>
+          <t>كارما محمد حسام</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>Lojain Walid Mohamed</t>
+          <t>Karma Mohamed Hossam</t>
         </is>
       </c>
       <c r="E108" s="12" t="inlineStr">
@@ -8419,17 +8419,17 @@
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-AR-005</t>
+          <t>SK-G4-LN-012</t>
         </is>
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t>محمد محمود الصياد</t>
+          <t>لوجين وليد محمد</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Mahmoud El-Sayad</t>
+          <t>Lojain Walid Mohamed</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G109" s="13" t="n">
@@ -8488,17 +8488,17 @@
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-AR-001</t>
+          <t>SK-G4-AR-0026</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>مها رضوان تسون</t>
+          <t>لينا بهاء</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>Maha Radwan Tsoun</t>
+          <t>Lina Bahaa</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">
@@ -8512,32 +8512,32 @@
         </is>
       </c>
       <c r="G110" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H110" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I110" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J110" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K110" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="L110" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M110" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="N110" s="16" t="n">
-        <v>136.5</v>
+        <v>140</v>
       </c>
       <c r="O110" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P110" s="16" t="inlineStr">
@@ -8557,17 +8557,17 @@
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-002</t>
+          <t>SK-G4-EN-3027</t>
         </is>
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>مهيب جمال فتح الله</t>
+          <t>محمد مازن شلار</t>
         </is>
       </c>
       <c r="D111" s="15" t="inlineStr">
         <is>
-          <t>Moheb Gamal Fathallah</t>
+          <t>Mohamed Malaz Shalar</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
@@ -8581,32 +8581,32 @@
         </is>
       </c>
       <c r="G111" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H111" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I111" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J111" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K111" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="L111" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M111" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="N111" s="16" t="n">
-        <v>136.5</v>
+        <v>140</v>
       </c>
       <c r="O111" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P111" s="16" t="inlineStr">
@@ -8626,17 +8626,17 @@
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-010</t>
+          <t>SK-G4-AR-005</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>ميرا محمد عطاها</t>
+          <t>محمد محمود الصياد</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>Mira Mohamed Ataha</t>
+          <t>Mohamed Mahmoud El-Sayad</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G112" s="13" t="n">
@@ -8695,17 +8695,17 @@
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-006</t>
+          <t>SK-G4-AR-9749</t>
         </is>
       </c>
       <c r="C113" s="14" t="inlineStr">
         <is>
-          <t>يحيي محمد فاروق</t>
+          <t>مرام شريف رجب</t>
         </is>
       </c>
       <c r="D113" s="15" t="inlineStr">
         <is>
-          <t>Yahia Mohamed Farouk</t>
+          <t>Maram Sheref Ragab</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
@@ -8715,36 +8715,36 @@
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G113" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H113" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I113" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J113" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K113" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="L113" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M113" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="N113" s="16" t="n">
-        <v>136.5</v>
+        <v>140</v>
       </c>
       <c r="O113" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P113" s="16" t="inlineStr">
@@ -8764,17 +8764,17 @@
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>SK-G4-LN-004</t>
+          <t>SK-G4-AR-001</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>يوسف كمال محمد</t>
+          <t>مها رضوان تسون</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>Youssef Kamal Mohamed</t>
+          <t>Maha Radwan Tsoun</t>
         </is>
       </c>
       <c r="E114" s="12" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G114" s="13" t="n">
@@ -8833,22 +8833,22 @@
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-005</t>
+          <t>SK-G4-LN-002</t>
         </is>
       </c>
       <c r="C115" s="14" t="inlineStr">
         <is>
-          <t>أيسل محمد السعيد</t>
+          <t>مهيب جمال فتح الله</t>
         </is>
       </c>
       <c r="D115" s="15" t="inlineStr">
         <is>
-          <t>Aysel Mohamed El-Saeed</t>
+          <t>Moheb Gamal Fathallah</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>الصف 5</t>
+          <t>الصف 4</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
@@ -8902,56 +8902,56 @@
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-003</t>
+          <t>SK-G4-LN-010</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>جودى مهند خضرو</t>
+          <t>ميرا محمد عطاها</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>Judi Mohannad Khidro</t>
+          <t>Mira Mohamed Ataha</t>
         </is>
       </c>
       <c r="E116" s="12" t="inlineStr">
         <is>
-          <t>الصف 5</t>
+          <t>الصف 4</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G116" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="H116" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="I116" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="J116" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="K116" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="L116" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="M116" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="N116" s="16" t="n">
-        <v>140</v>
+        <v>136.5</v>
       </c>
       <c r="O116" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="P116" s="16" t="inlineStr">
@@ -8971,56 +8971,56 @@
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-002</t>
+          <t>SK-G4-EN-6708</t>
         </is>
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>جويرية أحمد عطيه</t>
+          <t>يامن محمد رفعت</t>
         </is>
       </c>
       <c r="D117" s="15" t="inlineStr">
         <is>
-          <t>Jowairia Ahmed Attia</t>
+          <t>Yamen Mohamed Refaat</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>الصف 5</t>
+          <t>الصف 4</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G117" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H117" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I117" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J117" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K117" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="L117" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M117" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="N117" s="16" t="n">
-        <v>136.5</v>
+        <v>140</v>
       </c>
       <c r="O117" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P117" s="16" t="inlineStr">
@@ -9040,27 +9040,27 @@
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-006</t>
+          <t>SK-G4-LN-006</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>رفيدة خالد رجب</t>
+          <t>يحيي محمد فاروق</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>Rofayda Khaled Ragab</t>
+          <t>Yahia Mohamed Farouk</t>
         </is>
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>الصف 5</t>
+          <t>الصف 4</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G118" s="13" t="n">
@@ -9109,22 +9109,22 @@
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-004</t>
+          <t>SK-G4-LN-004</t>
         </is>
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>رقية رضا عبد المقصود</t>
+          <t>يوسف كمال محمد</t>
         </is>
       </c>
       <c r="D119" s="15" t="inlineStr">
         <is>
-          <t>Roqaya Reda Abdel Maqsoud</t>
+          <t>Youssef Kamal Mohamed</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>الصف 5</t>
+          <t>الصف 4</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
@@ -9178,17 +9178,17 @@
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-003</t>
+          <t>SK-G5-LN-005</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>رودينة عبد الله السيد</t>
+          <t>أيسل محمد السعيد</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>Rodaina Abdullah Sayed</t>
+          <t>Aysel Mohamed El-Saeed</t>
         </is>
       </c>
       <c r="E120" s="12" t="inlineStr">
@@ -9247,17 +9247,17 @@
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-007</t>
+          <t>SK-G5-AR-003</t>
         </is>
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>زياد مصطفى فرج</t>
+          <t>جودى مهند خضرو</t>
         </is>
       </c>
       <c r="D121" s="15" t="inlineStr">
         <is>
-          <t>Ziad Mostafa Farag</t>
+          <t>Judi Mohannad Khidro</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
@@ -9271,32 +9271,32 @@
         </is>
       </c>
       <c r="G121" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H121" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I121" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J121" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K121" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="L121" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M121" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="N121" s="16" t="n">
-        <v>136.5</v>
+        <v>140</v>
       </c>
       <c r="O121" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P121" s="16" t="inlineStr">
@@ -9316,17 +9316,17 @@
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-009</t>
+          <t>SK-G5-AR-002</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>سامح طه النقاش</t>
+          <t>جويرية أحمد عطيه</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>Sameh Taha El-Naqqash</t>
+          <t>Jowairia Ahmed Attia</t>
         </is>
       </c>
       <c r="E122" s="12" t="inlineStr">
@@ -9385,17 +9385,17 @@
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-002</t>
+          <t>SK-G5-AR-006</t>
         </is>
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>عائشة محمد علاء الدين</t>
+          <t>رفيدة خالد رجب</t>
         </is>
       </c>
       <c r="D123" s="15" t="inlineStr">
         <is>
-          <t>Aisha Mohamed Alaa El-Din</t>
+          <t>Rofayda Khaled Ragab</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G123" s="13" t="n">
@@ -9454,17 +9454,17 @@
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-008</t>
+          <t>SK-G5-LN-004</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>عبد الله محمود الصياد</t>
+          <t>رقية رضا عبد المقصود</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>Abdullah Mahmoud El-Sayad</t>
+          <t>Roqaya Reda Abdel Maqsoud</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G124" s="13" t="n">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-001</t>
+          <t>SK-G5-LN-003</t>
         </is>
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>كيان محمود منصور</t>
+          <t>رودينة عبد الله السيد</t>
         </is>
       </c>
       <c r="D125" s="15" t="inlineStr">
         <is>
-          <t>Kayan Mahmoud Mansour</t>
+          <t>Rodaina Abdullah Sayed</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G125" s="13" t="n">
@@ -9592,17 +9592,17 @@
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-001</t>
+          <t>SK-G5-AR-007</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>لينا أحمد شوقى</t>
+          <t>زياد مصطفى فرج</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>Lina Ahmed Shawky</t>
+          <t>Ziad Mostafa Farag</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G126" s="13" t="n">
@@ -9661,17 +9661,17 @@
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-005</t>
+          <t>SK-G5-AR-009</t>
         </is>
       </c>
       <c r="C127" s="14" t="inlineStr">
         <is>
-          <t>ليندا هشام أحمد</t>
+          <t>سامح طه النقاش</t>
         </is>
       </c>
       <c r="D127" s="15" t="inlineStr">
         <is>
-          <t>Linda Hesham Ahmed</t>
+          <t>Sameh Taha El-Naqqash</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
@@ -9730,17 +9730,17 @@
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-009</t>
+          <t>SK-G5-LN-002</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>محمد أدهم حربي</t>
+          <t>عائشة محمد علاء الدين</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Adham Harby</t>
+          <t>Aisha Mohamed Alaa El-Din</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
@@ -9799,17 +9799,17 @@
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-008</t>
+          <t>SK-G5-AR-008</t>
         </is>
       </c>
       <c r="C129" s="14" t="inlineStr">
         <is>
-          <t>محمد عمرو محمد</t>
+          <t>عبد الله محمود الصياد</t>
         </is>
       </c>
       <c r="D129" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Amr Mohamed</t>
+          <t>Abdullah Mahmoud El-Sayad</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G129" s="13" t="n">
@@ -9868,17 +9868,17 @@
       </c>
       <c r="B130" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-007</t>
+          <t>SK-G5-AR-001</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>مريم حمدى أحمد</t>
+          <t>كيان محمود منصور</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>Mariam Hamdy Ahmed</t>
+          <t>Kayan Mahmoud Mansour</t>
         </is>
       </c>
       <c r="E130" s="12" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G130" s="13" t="n">
@@ -9937,17 +9937,17 @@
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-010</t>
+          <t>SK-G5-LN-001</t>
         </is>
       </c>
       <c r="C131" s="14" t="inlineStr">
         <is>
-          <t>مصطفى أحمد مصطفى</t>
+          <t>لينا أحمد شوقى</t>
         </is>
       </c>
       <c r="D131" s="15" t="inlineStr">
         <is>
-          <t>Mostafa Ahmed Mostafa</t>
+          <t>Lina Ahmed Shawky</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G131" s="13" t="n">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-AR-004</t>
+          <t>SK-G5-AR-005</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>ملك محمد</t>
+          <t>ليندا هشام أحمد</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>Malak Mohamed</t>
+          <t>Linda Hesham Ahmed</t>
         </is>
       </c>
       <c r="E132" s="12" t="inlineStr">
@@ -10030,32 +10030,32 @@
         </is>
       </c>
       <c r="G132" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="H132" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="I132" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="J132" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="K132" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="L132" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="M132" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="N132" s="16" t="n">
-        <v>140</v>
+        <v>136.5</v>
       </c>
       <c r="O132" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="P132" s="16" t="inlineStr">
@@ -10075,17 +10075,17 @@
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>SK-G5-LN-006</t>
+          <t>SK-G5-LN-009</t>
         </is>
       </c>
       <c r="C133" s="14" t="inlineStr">
         <is>
-          <t>مليكة محمد نوار</t>
+          <t>محمد أدهم حربي</t>
         </is>
       </c>
       <c r="D133" s="15" t="inlineStr">
         <is>
-          <t>Malika Mohamed Nawar</t>
+          <t>Mohamed Adham Harby</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
@@ -10144,22 +10144,22 @@
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-005</t>
+          <t>SK-G5-LN-008</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>أروى محمد أحمد</t>
+          <t>محمد عمرو محمد</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>Arwa Mohamed Ahmed</t>
+          <t>Mohamed Amr Mohamed</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>الصف 6</t>
+          <t>الصف 5</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
@@ -10213,27 +10213,27 @@
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-AR-004</t>
+          <t>SK-G5-LN-007</t>
         </is>
       </c>
       <c r="C135" s="14" t="inlineStr">
         <is>
-          <t>أسيل حمد أحمد</t>
+          <t>مريم حمدى أحمد</t>
         </is>
       </c>
       <c r="D135" s="15" t="inlineStr">
         <is>
-          <t>Aseel Hamad Ahmed</t>
+          <t>Mariam Hamdy Ahmed</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>الصف 6</t>
+          <t>الصف 5</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G135" s="13" t="n">
@@ -10282,27 +10282,27 @@
       </c>
       <c r="B136" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-011</t>
+          <t>SK-G5-AR-010</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>أفنان أحمد</t>
+          <t>مصطفى أحمد مصطفى</t>
         </is>
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>Afnan Ahmed</t>
+          <t>Mostafa Ahmed Mostafa</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
-          <t>الصف 6</t>
+          <t>الصف 5</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G136" s="13" t="n">
@@ -10351,22 +10351,22 @@
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-AR-003</t>
+          <t>SK-G5-AR-004</t>
         </is>
       </c>
       <c r="C137" s="14" t="inlineStr">
         <is>
-          <t>باسم حسن العمري</t>
+          <t>ملك محمد</t>
         </is>
       </c>
       <c r="D137" s="15" t="inlineStr">
         <is>
-          <t>Bassem Hassan El-Omari</t>
+          <t>Malak Mohamed</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>الصف 6</t>
+          <t>الصف 5</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
@@ -10375,32 +10375,32 @@
         </is>
       </c>
       <c r="G137" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H137" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I137" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J137" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K137" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="L137" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M137" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="N137" s="16" t="n">
-        <v>136.5</v>
+        <v>140</v>
       </c>
       <c r="O137" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P137" s="16" t="inlineStr">
@@ -10420,22 +10420,22 @@
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-002</t>
+          <t>SK-G5-LN-006</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>سيف جمال إسماعيل</t>
+          <t>مليكة محمد نوار</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>Seif Gamal Ismail</t>
+          <t>Malika Mohamed Nawar</t>
         </is>
       </c>
       <c r="E138" s="12" t="inlineStr">
         <is>
-          <t>الصف 6</t>
+          <t>الصف 5</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr">
@@ -10489,17 +10489,17 @@
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-010</t>
+          <t>SK-G6-LN-005</t>
         </is>
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>لارين أحمد الشوني</t>
+          <t>أروى محمد أحمد</t>
         </is>
       </c>
       <c r="D139" s="15" t="inlineStr">
         <is>
-          <t>Lareen Ahmed El-Shouny</t>
+          <t>Arwa Mohamed Ahmed</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
@@ -10558,17 +10558,17 @@
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-009</t>
+          <t>SK-G6-AR-004</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>لورين وليد محمد</t>
+          <t>أسيل حمد أحمد</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>Loreen Walid Mohamed</t>
+          <t>Aseel Hamad Ahmed</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G140" s="13" t="n">
@@ -10627,17 +10627,17 @@
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-008</t>
+          <t>SK-G6-LN-011</t>
         </is>
       </c>
       <c r="C141" s="14" t="inlineStr">
         <is>
-          <t>ليان السيد على</t>
+          <t>أفنان أحمد</t>
         </is>
       </c>
       <c r="D141" s="15" t="inlineStr">
         <is>
-          <t>Layan Elsayed Ali</t>
+          <t>Afnan Ahmed</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr">
@@ -10696,17 +10696,17 @@
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-006</t>
+          <t>SK-G6-AR-003</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>ليليا مازن شلار</t>
+          <t>باسم حسن العمري</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>Lilia Mazen Shollar</t>
+          <t>Bassem Hassan El-Omari</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="F142" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G142" s="13" t="n">
@@ -10765,17 +10765,17 @@
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-AR-002</t>
+          <t>SK-G6-LN-002</t>
         </is>
       </c>
       <c r="C143" s="14" t="inlineStr">
         <is>
-          <t>لينا هشام أحمد</t>
+          <t>سيف جمال إسماعيل</t>
         </is>
       </c>
       <c r="D143" s="15" t="inlineStr">
         <is>
-          <t>Lina Hesham Ahmed</t>
+          <t>Seif Gamal Ismail</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
@@ -10785,36 +10785,36 @@
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G143" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="H143" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="I143" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="J143" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="K143" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="L143" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="M143" s="13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="N143" s="16" t="n">
-        <v>140</v>
+        <v>136.5</v>
       </c>
       <c r="O143" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="P143" s="16" t="inlineStr">
@@ -10834,17 +10834,17 @@
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-007</t>
+          <t>SK-G6-LN-010</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>ماسة محمد أنور</t>
+          <t>لارين أحمد الشوني</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>Massa Mohamed Anwar</t>
+          <t>Lareen Ahmed El-Shouny</t>
         </is>
       </c>
       <c r="E144" s="12" t="inlineStr">
@@ -10903,17 +10903,17 @@
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-003</t>
+          <t>SK-G6-LN-009</t>
         </is>
       </c>
       <c r="C145" s="14" t="inlineStr">
         <is>
-          <t>مالك محمود عبد الحميد</t>
+          <t>لورين وليد محمد</t>
         </is>
       </c>
       <c r="D145" s="15" t="inlineStr">
         <is>
-          <t>Malek Mahmoud Abdel Hamid</t>
+          <t>Loreen Walid Mohamed</t>
         </is>
       </c>
       <c r="E145" s="12" t="inlineStr">
@@ -10972,17 +10972,17 @@
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-001</t>
+          <t>SK-G6-LN-008</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>محمد السيد سمير</t>
+          <t>ليان السيد على</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Elsayed Samir</t>
+          <t>Layan Elsayed Ali</t>
         </is>
       </c>
       <c r="E146" s="12" t="inlineStr">
@@ -11041,17 +11041,17 @@
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-LN-004</t>
+          <t>SK-G6-LN-006</t>
         </is>
       </c>
       <c r="C147" s="14" t="inlineStr">
         <is>
-          <t>محمد مصطفى وحيد</t>
+          <t>ليليا مازن شلار</t>
         </is>
       </c>
       <c r="D147" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Mostafa Waheed</t>
+          <t>Lilia Mazen Shollar</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr">
@@ -11110,17 +11110,17 @@
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-AR-005</t>
+          <t>SK-G6-AR-002</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr">
         <is>
-          <t>هدى محمد مجدى</t>
+          <t>لينا هشام أحمد</t>
         </is>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>Hoda Mohamed Magdy</t>
+          <t>Lina Hesham Ahmed</t>
         </is>
       </c>
       <c r="E148" s="12" t="inlineStr">
@@ -11134,32 +11134,32 @@
         </is>
       </c>
       <c r="G148" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H148" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I148" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J148" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K148" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="L148" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M148" s="13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="N148" s="16" t="n">
-        <v>136.5</v>
+        <v>140</v>
       </c>
       <c r="O148" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P148" s="16" t="inlineStr">
@@ -11179,17 +11179,17 @@
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>SK-G6-AR-001</t>
+          <t>SK-G6-LN-007</t>
         </is>
       </c>
       <c r="C149" s="14" t="inlineStr">
         <is>
-          <t>ياسين إسلام حمد</t>
+          <t>ماسة محمد أنور</t>
         </is>
       </c>
       <c r="D149" s="15" t="inlineStr">
         <is>
-          <t>Yaseen Islam Hamad</t>
+          <t>Massa Mohamed Anwar</t>
         </is>
       </c>
       <c r="E149" s="12" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G149" s="13" t="n">
@@ -11248,22 +11248,22 @@
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-008</t>
+          <t>SK-G6-LN-003</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr">
         <is>
-          <t>آدم عبد الحميد عيد</t>
+          <t>مالك محمود عبد الحميد</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>Adam Abdel Hamid Eid</t>
+          <t>Malek Mahmoud Abdel Hamid</t>
         </is>
       </c>
       <c r="E150" s="12" t="inlineStr">
         <is>
-          <t>الصف 7</t>
+          <t>الصف 6</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
@@ -11317,27 +11317,27 @@
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-AR-006</t>
+          <t>SK-G6-LN-001</t>
         </is>
       </c>
       <c r="C151" s="14" t="inlineStr">
         <is>
-          <t>بلال محمد عادل</t>
+          <t>محمد السيد سمير</t>
         </is>
       </c>
       <c r="D151" s="15" t="inlineStr">
         <is>
-          <t>Belal Mohamed Adel</t>
+          <t>Mohamed Elsayed Samir</t>
         </is>
       </c>
       <c r="E151" s="12" t="inlineStr">
         <is>
-          <t>الصف 7</t>
+          <t>الصف 6</t>
         </is>
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G151" s="13" t="n">
@@ -11386,22 +11386,22 @@
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-003</t>
+          <t>SK-G6-LN-004</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr">
         <is>
-          <t>تقى أحمد محمود</t>
+          <t>محمد مصطفى وحيد</t>
         </is>
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>Toqa Ahmed Mahmoud</t>
+          <t>Mohamed Mostafa Waheed</t>
         </is>
       </c>
       <c r="E152" s="12" t="inlineStr">
         <is>
-          <t>الصف 7</t>
+          <t>الصف 6</t>
         </is>
       </c>
       <c r="F152" s="12" t="inlineStr">
@@ -11455,27 +11455,27 @@
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-004</t>
+          <t>SK-G6-AR-005</t>
         </is>
       </c>
       <c r="C153" s="14" t="inlineStr">
         <is>
-          <t>جودى خالد رجب</t>
+          <t>هدى محمد مجدى</t>
         </is>
       </c>
       <c r="D153" s="15" t="inlineStr">
         <is>
-          <t>Judy Khaled Ragab</t>
+          <t>Hoda Mohamed Magdy</t>
         </is>
       </c>
       <c r="E153" s="12" t="inlineStr">
         <is>
-          <t>الصف 7</t>
+          <t>الصف 6</t>
         </is>
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G153" s="13" t="n">
@@ -11524,22 +11524,22 @@
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-AR-004</t>
+          <t>SK-G6-AR-001</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr">
         <is>
-          <t>سارة أحمد مصطفى</t>
+          <t>ياسين إسلام حمد</t>
         </is>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>Sara Ahmed Mostafa</t>
+          <t>Yaseen Islam Hamad</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr">
         <is>
-          <t>الصف 7</t>
+          <t>الصف 6</t>
         </is>
       </c>
       <c r="F154" s="12" t="inlineStr">
@@ -11593,17 +11593,17 @@
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-AR-005</t>
+          <t>SK-G7-LN-008</t>
         </is>
       </c>
       <c r="C155" s="14" t="inlineStr">
         <is>
-          <t>عمار محمود سعد</t>
+          <t>آدم عبد الحميد عيد</t>
         </is>
       </c>
       <c r="D155" s="15" t="inlineStr">
         <is>
-          <t>Ammar Mahmoud Saad</t>
+          <t>Adam Abdel Hamid Eid</t>
         </is>
       </c>
       <c r="E155" s="12" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G155" s="13" t="n">
@@ -11662,17 +11662,17 @@
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-007</t>
+          <t>SK-G7-AR-006</t>
         </is>
       </c>
       <c r="C156" s="14" t="inlineStr">
         <is>
-          <t>عمر أحمد عصام</t>
+          <t>بلال محمد عادل</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>Omar Ahmed Essam</t>
+          <t>Belal Mohamed Adel</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G156" s="13" t="n">
@@ -11731,17 +11731,17 @@
       </c>
       <c r="B157" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-AR-003</t>
+          <t>SK-G7-LN-003</t>
         </is>
       </c>
       <c r="C157" s="14" t="inlineStr">
         <is>
-          <t>فريدة شريف رجب</t>
+          <t>تقى أحمد محمود</t>
         </is>
       </c>
       <c r="D157" s="15" t="inlineStr">
         <is>
-          <t>Farida Sherif Ragab</t>
+          <t>Toqa Ahmed Mahmoud</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G157" s="13" t="n">
@@ -11800,17 +11800,17 @@
       </c>
       <c r="B158" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-AR-002</t>
+          <t>SK-G7-LN-004</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr">
         <is>
-          <t>ليان محمود رزق</t>
+          <t>جودى خالد رجب</t>
         </is>
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>Layan Mahmoud Rezk</t>
+          <t>Judy Khaled Ragab</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="F158" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G158" s="13" t="n">
@@ -11869,17 +11869,17 @@
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-006</t>
+          <t>SK-G7-AR-004</t>
         </is>
       </c>
       <c r="C159" s="14" t="inlineStr">
         <is>
-          <t>مالك أدهم حربي</t>
+          <t>سارة أحمد مصطفى</t>
         </is>
       </c>
       <c r="D159" s="15" t="inlineStr">
         <is>
-          <t>Malek Adham Harby</t>
+          <t>Sara Ahmed Mostafa</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G159" s="13" t="n">
@@ -11938,17 +11938,17 @@
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-001</t>
+          <t>SK-G7-AR-005</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr">
         <is>
-          <t>مايا هيثم رشوان</t>
+          <t>عمار محمود سعد</t>
         </is>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>Maya Haitham Rashwan</t>
+          <t>Ammar Mahmoud Saad</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="F160" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G160" s="13" t="n">
@@ -12007,17 +12007,17 @@
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-002</t>
+          <t>SK-G7-LN-007</t>
         </is>
       </c>
       <c r="C161" s="14" t="inlineStr">
         <is>
-          <t>مريم أدهم حربي</t>
+          <t>عمر أحمد عصام</t>
         </is>
       </c>
       <c r="D161" s="15" t="inlineStr">
         <is>
-          <t>Mariam Adham Harby</t>
+          <t>Omar Ahmed Essam</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr">
@@ -12076,17 +12076,17 @@
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-AR-001</t>
+          <t>SK-G7-AR-003</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr">
         <is>
-          <t>نورسان إسلام محمد</t>
+          <t>فريدة شريف رجب</t>
         </is>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>Noursan Islam Mohamed</t>
+          <t>Farida Sherif Ragab</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
@@ -12145,17 +12145,17 @@
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t>SK-G7-LN-005</t>
+          <t>SK-G7-AR-002</t>
         </is>
       </c>
       <c r="C163" s="14" t="inlineStr">
         <is>
-          <t>ياسين سليمان محمد</t>
+          <t>ليان محمود رزق</t>
         </is>
       </c>
       <c r="D163" s="15" t="inlineStr">
         <is>
-          <t>Yaseen Soliman Mohamed</t>
+          <t>Layan Mahmoud Rezk</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G163" s="13" t="n">
@@ -12214,22 +12214,22 @@
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>SK-G8-LN-001</t>
+          <t>SK-G7-LN-006</t>
         </is>
       </c>
       <c r="C164" s="14" t="inlineStr">
         <is>
-          <t>بسملة عبد الله سيد</t>
+          <t>مالك أدهم حربي</t>
         </is>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>Basmala Abdullah Sayed</t>
+          <t>Malek Adham Harby</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr">
         <is>
-          <t>الصف 8</t>
+          <t>الصف 7</t>
         </is>
       </c>
       <c r="F164" s="12" t="inlineStr">
@@ -12283,27 +12283,27 @@
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>SK-G8-AR-002</t>
+          <t>SK-G7-LN-001</t>
         </is>
       </c>
       <c r="C165" s="14" t="inlineStr">
         <is>
-          <t>سجد محمود منصور</t>
+          <t>مايا هيثم رشوان</t>
         </is>
       </c>
       <c r="D165" s="15" t="inlineStr">
         <is>
-          <t>Saged Mahmoud Mansour</t>
+          <t>Maya Haitham Rashwan</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>الصف 8</t>
+          <t>الصف 7</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G165" s="13" t="n">
@@ -12352,27 +12352,27 @@
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t>SK-G8-AR-003</t>
+          <t>SK-G7-LN-002</t>
         </is>
       </c>
       <c r="C166" s="14" t="inlineStr">
         <is>
-          <t>عبد الغني عصام عبد الله</t>
+          <t>مريم أدهم حربي</t>
         </is>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>Abdel Ghany Essam Abdullah</t>
+          <t>Mariam Adham Harby</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr">
         <is>
-          <t>الصف 8</t>
+          <t>الصف 7</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G166" s="13" t="n">
@@ -12421,22 +12421,22 @@
       </c>
       <c r="B167" s="13" t="inlineStr">
         <is>
-          <t>SK-G8-AR-001</t>
+          <t>SK-G7-AR-001</t>
         </is>
       </c>
       <c r="C167" s="14" t="inlineStr">
         <is>
-          <t>محمد حسن العمري</t>
+          <t>نورسان إسلام محمد</t>
         </is>
       </c>
       <c r="D167" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Hassan El-Omari</t>
+          <t>Noursan Islam Mohamed</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>الصف 8</t>
+          <t>الصف 7</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
@@ -12490,22 +12490,22 @@
       </c>
       <c r="B168" s="13" t="inlineStr">
         <is>
-          <t>SK-G8-LN-002</t>
+          <t>SK-G7-LN-005</t>
         </is>
       </c>
       <c r="C168" s="14" t="inlineStr">
         <is>
-          <t>وتين أحمد الشوني</t>
+          <t>ياسين سليمان محمد</t>
         </is>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>Wateen Ahmed El-Shouny</t>
+          <t>Yaseen Soliman Mohamed</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
         <is>
-          <t>الصف 8</t>
+          <t>الصف 7</t>
         </is>
       </c>
       <c r="F168" s="12" t="inlineStr">
@@ -12559,22 +12559,22 @@
       </c>
       <c r="B169" s="13" t="inlineStr">
         <is>
-          <t>SK-G9-LN-001</t>
+          <t>SK-G8-LN-001</t>
         </is>
       </c>
       <c r="C169" s="14" t="inlineStr">
         <is>
-          <t>أحمد رضا شوشة</t>
+          <t>بسملة عبد الله سيد</t>
         </is>
       </c>
       <c r="D169" s="15" t="inlineStr">
         <is>
-          <t>Ahmed Reda Shousha</t>
+          <t>Basmala Abdullah Sayed</t>
         </is>
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>الصف 9</t>
+          <t>الصف 8</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
@@ -12628,22 +12628,22 @@
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
-          <t>SK-G9-AR-002</t>
+          <t>SK-G8-AR-002</t>
         </is>
       </c>
       <c r="C170" s="14" t="inlineStr">
         <is>
-          <t>أيمن عصام القاضي</t>
+          <t>سجد محمود منصور</t>
         </is>
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>Ayman Essam El-Kady</t>
+          <t>Saged Mahmoud Mansour</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
         <is>
-          <t>الصف 9</t>
+          <t>الصف 8</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
@@ -12697,27 +12697,27 @@
       </c>
       <c r="B171" s="13" t="inlineStr">
         <is>
-          <t>SK-G9-LN-002</t>
+          <t>SK-G8-AR-003</t>
         </is>
       </c>
       <c r="C171" s="14" t="inlineStr">
         <is>
-          <t>جودى هيثم رشوان</t>
+          <t>عبد الغني عصام عبد الله</t>
         </is>
       </c>
       <c r="D171" s="15" t="inlineStr">
         <is>
-          <t>Judy Haitham Rashwan</t>
+          <t>Abdel Ghany Essam Abdullah</t>
         </is>
       </c>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>الصف 9</t>
+          <t>الصف 8</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G171" s="13" t="n">
@@ -12766,22 +12766,22 @@
       </c>
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>SK-G9-AR-001</t>
+          <t>SK-G8-AR-001</t>
         </is>
       </c>
       <c r="C172" s="14" t="inlineStr">
         <is>
-          <t>ساره محمد عطاها</t>
+          <t>محمد حسن العمري</t>
         </is>
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>Sara Mohamed Ataha</t>
+          <t>Mohamed Hassan El-Omari</t>
         </is>
       </c>
       <c r="E172" s="12" t="inlineStr">
         <is>
-          <t>الصف 9</t>
+          <t>الصف 8</t>
         </is>
       </c>
       <c r="F172" s="12" t="inlineStr">
@@ -12835,27 +12835,27 @@
       </c>
       <c r="B173" s="13" t="inlineStr">
         <is>
-          <t>SK-G9-AR-003</t>
+          <t>SK-G8-LN-002</t>
         </is>
       </c>
       <c r="C173" s="14" t="inlineStr">
         <is>
-          <t>محمد عبد الله النقاش</t>
+          <t>وتين أحمد الشوني</t>
         </is>
       </c>
       <c r="D173" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Abdullah El-Nakkash</t>
+          <t>Wateen Ahmed El-Shouny</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>الصف 9</t>
+          <t>الصف 8</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G173" s="13" t="n">
@@ -12895,6 +12895,351 @@
       <c r="Q173" s="16" t="inlineStr">
         <is>
           <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="12" t="n">
+        <v>170</v>
+      </c>
+      <c r="B174" s="13" t="inlineStr">
+        <is>
+          <t>SK-G9-LN-001</t>
+        </is>
+      </c>
+      <c r="C174" s="14" t="inlineStr">
+        <is>
+          <t>أحمد رضا شوشة</t>
+        </is>
+      </c>
+      <c r="D174" s="15" t="inlineStr">
+        <is>
+          <t>Ahmed Reda Shousha</t>
+        </is>
+      </c>
+      <c r="E174" s="12" t="inlineStr">
+        <is>
+          <t>الصف 9</t>
+        </is>
+      </c>
+      <c r="F174" s="12" t="inlineStr">
+        <is>
+          <t>لغات</t>
+        </is>
+      </c>
+      <c r="G174" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H174" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I174" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J174" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K174" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L174" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M174" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="N174" s="16" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="O174" s="16" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="P174" s="16" t="inlineStr">
+        <is>
+          <t>ممتاز 🌟</t>
+        </is>
+      </c>
+      <c r="Q174" s="16" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="12" t="n">
+        <v>171</v>
+      </c>
+      <c r="B175" s="13" t="inlineStr">
+        <is>
+          <t>SK-G9-AR-002</t>
+        </is>
+      </c>
+      <c r="C175" s="14" t="inlineStr">
+        <is>
+          <t>أيمن عصام القاضي</t>
+        </is>
+      </c>
+      <c r="D175" s="15" t="inlineStr">
+        <is>
+          <t>Ayman Essam El-Kady</t>
+        </is>
+      </c>
+      <c r="E175" s="12" t="inlineStr">
+        <is>
+          <t>الصف 9</t>
+        </is>
+      </c>
+      <c r="F175" s="12" t="inlineStr">
+        <is>
+          <t>عربي</t>
+        </is>
+      </c>
+      <c r="G175" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H175" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I175" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J175" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K175" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L175" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M175" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="N175" s="16" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="O175" s="16" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="P175" s="16" t="inlineStr">
+        <is>
+          <t>ممتاز 🌟</t>
+        </is>
+      </c>
+      <c r="Q175" s="16" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="12" t="n">
+        <v>172</v>
+      </c>
+      <c r="B176" s="13" t="inlineStr">
+        <is>
+          <t>SK-G9-LN-002</t>
+        </is>
+      </c>
+      <c r="C176" s="14" t="inlineStr">
+        <is>
+          <t>جودى هيثم رشوان</t>
+        </is>
+      </c>
+      <c r="D176" s="15" t="inlineStr">
+        <is>
+          <t>Judy Haitham Rashwan</t>
+        </is>
+      </c>
+      <c r="E176" s="12" t="inlineStr">
+        <is>
+          <t>الصف 9</t>
+        </is>
+      </c>
+      <c r="F176" s="12" t="inlineStr">
+        <is>
+          <t>لغات</t>
+        </is>
+      </c>
+      <c r="G176" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H176" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I176" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J176" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K176" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L176" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M176" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="N176" s="16" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="O176" s="16" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="P176" s="16" t="inlineStr">
+        <is>
+          <t>ممتاز 🌟</t>
+        </is>
+      </c>
+      <c r="Q176" s="16" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="12" t="n">
+        <v>173</v>
+      </c>
+      <c r="B177" s="13" t="inlineStr">
+        <is>
+          <t>SK-G9-AR-001</t>
+        </is>
+      </c>
+      <c r="C177" s="14" t="inlineStr">
+        <is>
+          <t>ساره محمد عطاها</t>
+        </is>
+      </c>
+      <c r="D177" s="15" t="inlineStr">
+        <is>
+          <t>Sara Mohamed Ataha</t>
+        </is>
+      </c>
+      <c r="E177" s="12" t="inlineStr">
+        <is>
+          <t>الصف 9</t>
+        </is>
+      </c>
+      <c r="F177" s="12" t="inlineStr">
+        <is>
+          <t>عربي</t>
+        </is>
+      </c>
+      <c r="G177" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H177" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I177" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J177" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K177" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L177" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M177" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="N177" s="16" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="O177" s="16" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="P177" s="16" t="inlineStr">
+        <is>
+          <t>ممتاز 🌟</t>
+        </is>
+      </c>
+      <c r="Q177" s="16" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1">
+      <c r="A178" s="12" t="n">
+        <v>174</v>
+      </c>
+      <c r="B178" s="13" t="inlineStr">
+        <is>
+          <t>SK-G9-AR-003</t>
+        </is>
+      </c>
+      <c r="C178" s="14" t="inlineStr">
+        <is>
+          <t>محمد عبد الله النقاش</t>
+        </is>
+      </c>
+      <c r="D178" s="15" t="inlineStr">
+        <is>
+          <t>Mohamed Abdullah El-Nakkash</t>
+        </is>
+      </c>
+      <c r="E178" s="12" t="inlineStr">
+        <is>
+          <t>الصف 9</t>
+        </is>
+      </c>
+      <c r="F178" s="12" t="inlineStr">
+        <is>
+          <t>عربي</t>
+        </is>
+      </c>
+      <c r="G178" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H178" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I178" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J178" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K178" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L178" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M178" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="N178" s="16" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="O178" s="16" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="P178" s="16" t="inlineStr">
+        <is>
+          <t>ممتاز 🌟</t>
+        </is>
+      </c>
+      <c r="Q178" s="16" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -12913,8 +13258,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J170"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:J175"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -17758,12 +18103,12 @@
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-007</t>
+          <t>SK-G4-EN-6103</t>
         </is>
       </c>
       <c r="C98" s="18" t="inlineStr">
         <is>
-          <t>ريان عبد الرحمن</t>
+          <t>روفان عمر عبد المقصود</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -17796,11 +18141,7 @@
           <t>مقيد ومنتظم</t>
         </is>
       </c>
-      <c r="J98" s="12" t="inlineStr">
-        <is>
-          <t>سجلات معتمدة 2026</t>
-        </is>
-      </c>
+      <c r="J98" s="12" t="inlineStr"/>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="12" t="n">
@@ -17808,12 +18149,12 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-AR-006</t>
+          <t>SK-G4-LN-007</t>
         </is>
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>عبد الله مروان الشيخ</t>
+          <t>ريان عبد الرحمن</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
@@ -17828,7 +18169,7 @@
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -17858,12 +18199,12 @@
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-AR-004</t>
+          <t>SK-G4-AR-006</t>
         </is>
       </c>
       <c r="C100" s="18" t="inlineStr">
         <is>
-          <t>على شريف على</t>
+          <t>عبد الله مروان الشيخ</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
@@ -17908,12 +18249,12 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-005</t>
+          <t>SK-G4-AR-004</t>
         </is>
       </c>
       <c r="C101" s="18" t="inlineStr">
         <is>
-          <t>عمر أحمد الجزيرى</t>
+          <t>على شريف على</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
@@ -17928,7 +18269,7 @@
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -17958,12 +18299,12 @@
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-011</t>
+          <t>SK-G4-LN-005</t>
         </is>
       </c>
       <c r="C102" s="18" t="inlineStr">
         <is>
-          <t>فيروز هشام محمد</t>
+          <t>عمر أحمد الجزيرى</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -18008,12 +18349,12 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-AR-002</t>
+          <t>SK-G4-LN-011</t>
         </is>
       </c>
       <c r="C103" s="18" t="inlineStr">
         <is>
-          <t>كارما أحمد عطية</t>
+          <t>فيروز هشام محمد</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
@@ -18028,7 +18369,7 @@
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -18058,12 +18399,12 @@
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-009</t>
+          <t>SK-G4-AR-002</t>
         </is>
       </c>
       <c r="C104" s="18" t="inlineStr">
         <is>
-          <t>كارما محمد حسام</t>
+          <t>كارما أحمد عطية</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -18078,7 +18419,7 @@
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G104" s="12" t="inlineStr">
@@ -18108,12 +18449,12 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-012</t>
+          <t>SK-G4-LN-009</t>
         </is>
       </c>
       <c r="C105" s="18" t="inlineStr">
         <is>
-          <t>لوجين وليد محمد</t>
+          <t>كارما محمد حسام</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -18158,12 +18499,12 @@
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-AR-005</t>
+          <t>SK-G4-LN-012</t>
         </is>
       </c>
       <c r="C106" s="18" t="inlineStr">
         <is>
-          <t>محمد محمود الصياد</t>
+          <t>لوجين وليد محمد</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -18178,7 +18519,7 @@
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G106" s="12" t="inlineStr">
@@ -18208,12 +18549,12 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-AR-001</t>
+          <t>SK-G4-AR-0026</t>
         </is>
       </c>
       <c r="C107" s="18" t="inlineStr">
         <is>
-          <t>مها رضوان تسون</t>
+          <t>لينا بهاء</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
@@ -18246,11 +18587,7 @@
           <t>مقيد ومنتظم</t>
         </is>
       </c>
-      <c r="J107" s="12" t="inlineStr">
-        <is>
-          <t>سجلات معتمدة 2026</t>
-        </is>
-      </c>
+      <c r="J107" s="12" t="inlineStr"/>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="12" t="n">
@@ -18258,12 +18595,12 @@
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-002</t>
+          <t>SK-G4-EN-3027</t>
         </is>
       </c>
       <c r="C108" s="18" t="inlineStr">
         <is>
-          <t>مهيب جمال فتح الله</t>
+          <t>محمد مازن شلار</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -18296,11 +18633,7 @@
           <t>مقيد ومنتظم</t>
         </is>
       </c>
-      <c r="J108" s="12" t="inlineStr">
-        <is>
-          <t>سجلات معتمدة 2026</t>
-        </is>
-      </c>
+      <c r="J108" s="12" t="inlineStr"/>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="12" t="n">
@@ -18308,12 +18641,12 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-010</t>
+          <t>SK-G4-AR-005</t>
         </is>
       </c>
       <c r="C109" s="18" t="inlineStr">
         <is>
-          <t>ميرا محمد عطاها</t>
+          <t>محمد محمود الصياد</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
@@ -18328,7 +18661,7 @@
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
@@ -18358,12 +18691,12 @@
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-006</t>
+          <t>SK-G4-AR-9749</t>
         </is>
       </c>
       <c r="C110" s="18" t="inlineStr">
         <is>
-          <t>يحيي محمد فاروق</t>
+          <t>مرام شريف رجب</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
@@ -18378,7 +18711,7 @@
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G110" s="12" t="inlineStr">
@@ -18396,11 +18729,7 @@
           <t>مقيد ومنتظم</t>
         </is>
       </c>
-      <c r="J110" s="12" t="inlineStr">
-        <is>
-          <t>سجلات معتمدة 2026</t>
-        </is>
-      </c>
+      <c r="J110" s="12" t="inlineStr"/>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="12" t="n">
@@ -18408,12 +18737,12 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>SK-G4-LN-004</t>
+          <t>SK-G4-AR-001</t>
         </is>
       </c>
       <c r="C111" s="18" t="inlineStr">
         <is>
-          <t>يوسف كمال محمد</t>
+          <t>مها رضوان تسون</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
@@ -18428,7 +18757,7 @@
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
@@ -18458,12 +18787,12 @@
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-005</t>
+          <t>SK-G4-LN-002</t>
         </is>
       </c>
       <c r="C112" s="18" t="inlineStr">
         <is>
-          <t>أيسل محمد السعيد</t>
+          <t>مهيب جمال فتح الله</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
@@ -18473,7 +18802,7 @@
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>الصف 5</t>
+          <t>الصف 4</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
@@ -18508,12 +18837,12 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-003</t>
+          <t>SK-G4-LN-010</t>
         </is>
       </c>
       <c r="C113" s="18" t="inlineStr">
         <is>
-          <t>جودى مهند خضرو</t>
+          <t>ميرا محمد عطاها</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
@@ -18523,12 +18852,12 @@
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>الصف 5</t>
+          <t>الصف 4</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -18558,12 +18887,12 @@
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-002</t>
+          <t>SK-G4-EN-6708</t>
         </is>
       </c>
       <c r="C114" s="18" t="inlineStr">
         <is>
-          <t>جويرية أحمد عطيه</t>
+          <t>يامن محمد رفعت</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
@@ -18573,12 +18902,12 @@
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>الصف 5</t>
+          <t>الصف 4</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G114" s="12" t="inlineStr">
@@ -18596,11 +18925,7 @@
           <t>مقيد ومنتظم</t>
         </is>
       </c>
-      <c r="J114" s="12" t="inlineStr">
-        <is>
-          <t>سجلات معتمدة 2026</t>
-        </is>
-      </c>
+      <c r="J114" s="12" t="inlineStr"/>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="12" t="n">
@@ -18608,12 +18933,12 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-006</t>
+          <t>SK-G4-LN-006</t>
         </is>
       </c>
       <c r="C115" s="18" t="inlineStr">
         <is>
-          <t>رفيدة خالد رجب</t>
+          <t>يحيي محمد فاروق</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
@@ -18623,12 +18948,12 @@
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>الصف 5</t>
+          <t>الصف 4</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G115" s="12" t="inlineStr">
@@ -18658,12 +18983,12 @@
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-004</t>
+          <t>SK-G4-LN-004</t>
         </is>
       </c>
       <c r="C116" s="18" t="inlineStr">
         <is>
-          <t>رقية رضا عبد المقصود</t>
+          <t>يوسف كمال محمد</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
@@ -18673,7 +18998,7 @@
       </c>
       <c r="E116" s="12" t="inlineStr">
         <is>
-          <t>الصف 5</t>
+          <t>الصف 4</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
@@ -18708,12 +19033,12 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-003</t>
+          <t>SK-G5-LN-005</t>
         </is>
       </c>
       <c r="C117" s="18" t="inlineStr">
         <is>
-          <t>رودينة عبد الله السيد</t>
+          <t>أيسل محمد السعيد</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
@@ -18758,12 +19083,12 @@
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-007</t>
+          <t>SK-G5-AR-003</t>
         </is>
       </c>
       <c r="C118" s="18" t="inlineStr">
         <is>
-          <t>زياد مصطفى فرج</t>
+          <t>جودى مهند خضرو</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
@@ -18808,12 +19133,12 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-009</t>
+          <t>SK-G5-AR-002</t>
         </is>
       </c>
       <c r="C119" s="18" t="inlineStr">
         <is>
-          <t>سامح طه النقاش</t>
+          <t>جويرية أحمد عطيه</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
@@ -18858,12 +19183,12 @@
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-002</t>
+          <t>SK-G5-AR-006</t>
         </is>
       </c>
       <c r="C120" s="18" t="inlineStr">
         <is>
-          <t>عائشة محمد علاء الدين</t>
+          <t>رفيدة خالد رجب</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
@@ -18878,7 +19203,7 @@
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G120" s="12" t="inlineStr">
@@ -18908,12 +19233,12 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-008</t>
+          <t>SK-G5-LN-004</t>
         </is>
       </c>
       <c r="C121" s="18" t="inlineStr">
         <is>
-          <t>عبد الله محمود الصياد</t>
+          <t>رقية رضا عبد المقصود</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
@@ -18928,7 +19253,7 @@
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
@@ -18958,12 +19283,12 @@
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-001</t>
+          <t>SK-G5-LN-003</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>كيان محمود منصور</t>
+          <t>رودينة عبد الله السيد</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
@@ -18978,7 +19303,7 @@
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G122" s="12" t="inlineStr">
@@ -19008,12 +19333,12 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-001</t>
+          <t>SK-G5-AR-007</t>
         </is>
       </c>
       <c r="C123" s="18" t="inlineStr">
         <is>
-          <t>لينا أحمد شوقى</t>
+          <t>زياد مصطفى فرج</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
@@ -19028,7 +19353,7 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G123" s="12" t="inlineStr">
@@ -19058,12 +19383,12 @@
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-005</t>
+          <t>SK-G5-AR-009</t>
         </is>
       </c>
       <c r="C124" s="18" t="inlineStr">
         <is>
-          <t>ليندا هشام أحمد</t>
+          <t>سامح طه النقاش</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
@@ -19108,12 +19433,12 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-009</t>
+          <t>SK-G5-LN-002</t>
         </is>
       </c>
       <c r="C125" s="18" t="inlineStr">
         <is>
-          <t>محمد أدهم حربي</t>
+          <t>عائشة محمد علاء الدين</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
@@ -19158,12 +19483,12 @@
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-008</t>
+          <t>SK-G5-AR-008</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
         <is>
-          <t>محمد عمرو محمد</t>
+          <t>عبد الله محمود الصياد</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
@@ -19178,7 +19503,7 @@
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G126" s="12" t="inlineStr">
@@ -19208,12 +19533,12 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-007</t>
+          <t>SK-G5-AR-001</t>
         </is>
       </c>
       <c r="C127" s="18" t="inlineStr">
         <is>
-          <t>مريم حمدى أحمد</t>
+          <t>كيان محمود منصور</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
@@ -19228,7 +19553,7 @@
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
@@ -19258,12 +19583,12 @@
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-010</t>
+          <t>SK-G5-LN-001</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>مصطفى أحمد مصطفى</t>
+          <t>لينا أحمد شوقى</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
@@ -19278,7 +19603,7 @@
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G128" s="12" t="inlineStr">
@@ -19308,12 +19633,12 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-AR-004</t>
+          <t>SK-G5-AR-005</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>ملك محمد</t>
+          <t>ليندا هشام أحمد</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
@@ -19358,12 +19683,12 @@
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t>SK-G5-LN-006</t>
+          <t>SK-G5-LN-009</t>
         </is>
       </c>
       <c r="C130" s="18" t="inlineStr">
         <is>
-          <t>مليكة محمد نوار</t>
+          <t>محمد أدهم حربي</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
@@ -19408,12 +19733,12 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-005</t>
+          <t>SK-G5-LN-008</t>
         </is>
       </c>
       <c r="C131" s="18" t="inlineStr">
         <is>
-          <t>أروى محمد أحمد</t>
+          <t>محمد عمرو محمد</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
@@ -19423,7 +19748,7 @@
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>الصف 6</t>
+          <t>الصف 5</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
@@ -19458,12 +19783,12 @@
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-AR-004</t>
+          <t>SK-G5-LN-007</t>
         </is>
       </c>
       <c r="C132" s="18" t="inlineStr">
         <is>
-          <t>أسيل حمد أحمد</t>
+          <t>مريم حمدى أحمد</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
@@ -19473,12 +19798,12 @@
       </c>
       <c r="E132" s="12" t="inlineStr">
         <is>
-          <t>الصف 6</t>
+          <t>الصف 5</t>
         </is>
       </c>
       <c r="F132" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G132" s="12" t="inlineStr">
@@ -19508,12 +19833,12 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-011</t>
+          <t>SK-G5-AR-010</t>
         </is>
       </c>
       <c r="C133" s="18" t="inlineStr">
         <is>
-          <t>أفنان أحمد</t>
+          <t>مصطفى أحمد مصطفى</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
@@ -19523,12 +19848,12 @@
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>الصف 6</t>
+          <t>الصف 5</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
@@ -19558,12 +19883,12 @@
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-AR-003</t>
+          <t>SK-G5-AR-004</t>
         </is>
       </c>
       <c r="C134" s="18" t="inlineStr">
         <is>
-          <t>باسم حسن العمري</t>
+          <t>ملك محمد</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
@@ -19573,7 +19898,7 @@
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>الصف 6</t>
+          <t>الصف 5</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
@@ -19608,12 +19933,12 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-002</t>
+          <t>SK-G5-LN-006</t>
         </is>
       </c>
       <c r="C135" s="18" t="inlineStr">
         <is>
-          <t>سيف جمال إسماعيل</t>
+          <t>مليكة محمد نوار</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
@@ -19623,7 +19948,7 @@
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>الصف 6</t>
+          <t>الصف 5</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
@@ -19658,12 +19983,12 @@
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-010</t>
+          <t>SK-G6-LN-005</t>
         </is>
       </c>
       <c r="C136" s="18" t="inlineStr">
         <is>
-          <t>لارين أحمد الشوني</t>
+          <t>أروى محمد أحمد</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
@@ -19708,12 +20033,12 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-009</t>
+          <t>SK-G6-AR-004</t>
         </is>
       </c>
       <c r="C137" s="18" t="inlineStr">
         <is>
-          <t>لورين وليد محمد</t>
+          <t>أسيل حمد أحمد</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
@@ -19728,7 +20053,7 @@
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
@@ -19758,12 +20083,12 @@
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-008</t>
+          <t>SK-G6-LN-011</t>
         </is>
       </c>
       <c r="C138" s="18" t="inlineStr">
         <is>
-          <t>ليان السيد على</t>
+          <t>أفنان أحمد</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
@@ -19808,12 +20133,12 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-006</t>
+          <t>SK-G6-AR-003</t>
         </is>
       </c>
       <c r="C139" s="18" t="inlineStr">
         <is>
-          <t>ليليا مازن شلار</t>
+          <t>باسم حسن العمري</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
@@ -19828,7 +20153,7 @@
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -19858,12 +20183,12 @@
       </c>
       <c r="B140" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-AR-002</t>
+          <t>SK-G6-LN-002</t>
         </is>
       </c>
       <c r="C140" s="18" t="inlineStr">
         <is>
-          <t>لينا هشام أحمد</t>
+          <t>سيف جمال إسماعيل</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
@@ -19878,7 +20203,7 @@
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G140" s="12" t="inlineStr">
@@ -19908,12 +20233,12 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-007</t>
+          <t>SK-G6-LN-010</t>
         </is>
       </c>
       <c r="C141" s="18" t="inlineStr">
         <is>
-          <t>ماسة محمد أنور</t>
+          <t>لارين أحمد الشوني</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
@@ -19958,12 +20283,12 @@
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-003</t>
+          <t>SK-G6-LN-009</t>
         </is>
       </c>
       <c r="C142" s="18" t="inlineStr">
         <is>
-          <t>مالك محمود عبد الحميد</t>
+          <t>لورين وليد محمد</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
@@ -20008,12 +20333,12 @@
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-001</t>
+          <t>SK-G6-LN-008</t>
         </is>
       </c>
       <c r="C143" s="18" t="inlineStr">
         <is>
-          <t>محمد السيد سمير</t>
+          <t>ليان السيد على</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
@@ -20058,12 +20383,12 @@
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-LN-004</t>
+          <t>SK-G6-LN-006</t>
         </is>
       </c>
       <c r="C144" s="18" t="inlineStr">
         <is>
-          <t>محمد مصطفى وحيد</t>
+          <t>ليليا مازن شلار</t>
         </is>
       </c>
       <c r="D144" s="12" t="inlineStr">
@@ -20108,12 +20433,12 @@
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-AR-005</t>
+          <t>SK-G6-AR-002</t>
         </is>
       </c>
       <c r="C145" s="18" t="inlineStr">
         <is>
-          <t>هدى محمد مجدى</t>
+          <t>لينا هشام أحمد</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
@@ -20158,12 +20483,12 @@
       </c>
       <c r="B146" s="12" t="inlineStr">
         <is>
-          <t>SK-G6-AR-001</t>
+          <t>SK-G6-LN-007</t>
         </is>
       </c>
       <c r="C146" s="18" t="inlineStr">
         <is>
-          <t>ياسين إسلام حمد</t>
+          <t>ماسة محمد أنور</t>
         </is>
       </c>
       <c r="D146" s="12" t="inlineStr">
@@ -20178,7 +20503,7 @@
       </c>
       <c r="F146" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G146" s="12" t="inlineStr">
@@ -20208,12 +20533,12 @@
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-008</t>
+          <t>SK-G6-LN-003</t>
         </is>
       </c>
       <c r="C147" s="18" t="inlineStr">
         <is>
-          <t>آدم عبد الحميد عيد</t>
+          <t>مالك محمود عبد الحميد</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
@@ -20223,7 +20548,7 @@
       </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>الصف 7</t>
+          <t>الصف 6</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
@@ -20258,12 +20583,12 @@
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-AR-006</t>
+          <t>SK-G6-LN-001</t>
         </is>
       </c>
       <c r="C148" s="18" t="inlineStr">
         <is>
-          <t>بلال محمد عادل</t>
+          <t>محمد السيد سمير</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
@@ -20273,12 +20598,12 @@
       </c>
       <c r="E148" s="12" t="inlineStr">
         <is>
-          <t>الصف 7</t>
+          <t>الصف 6</t>
         </is>
       </c>
       <c r="F148" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G148" s="12" t="inlineStr">
@@ -20308,12 +20633,12 @@
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-003</t>
+          <t>SK-G6-LN-004</t>
         </is>
       </c>
       <c r="C149" s="18" t="inlineStr">
         <is>
-          <t>تقى أحمد محمود</t>
+          <t>محمد مصطفى وحيد</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
@@ -20323,7 +20648,7 @@
       </c>
       <c r="E149" s="12" t="inlineStr">
         <is>
-          <t>الصف 7</t>
+          <t>الصف 6</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
@@ -20358,12 +20683,12 @@
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-004</t>
+          <t>SK-G6-AR-005</t>
         </is>
       </c>
       <c r="C150" s="18" t="inlineStr">
         <is>
-          <t>جودى خالد رجب</t>
+          <t>هدى محمد مجدى</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
@@ -20373,12 +20698,12 @@
       </c>
       <c r="E150" s="12" t="inlineStr">
         <is>
-          <t>الصف 7</t>
+          <t>الصف 6</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G150" s="12" t="inlineStr">
@@ -20408,12 +20733,12 @@
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-AR-004</t>
+          <t>SK-G6-AR-001</t>
         </is>
       </c>
       <c r="C151" s="18" t="inlineStr">
         <is>
-          <t>سارة أحمد مصطفى</t>
+          <t>ياسين إسلام حمد</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
@@ -20423,7 +20748,7 @@
       </c>
       <c r="E151" s="12" t="inlineStr">
         <is>
-          <t>الصف 7</t>
+          <t>الصف 6</t>
         </is>
       </c>
       <c r="F151" s="12" t="inlineStr">
@@ -20458,12 +20783,12 @@
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-AR-005</t>
+          <t>SK-G7-LN-008</t>
         </is>
       </c>
       <c r="C152" s="18" t="inlineStr">
         <is>
-          <t>عمار محمود سعد</t>
+          <t>آدم عبد الحميد عيد</t>
         </is>
       </c>
       <c r="D152" s="12" t="inlineStr">
@@ -20478,7 +20803,7 @@
       </c>
       <c r="F152" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G152" s="12" t="inlineStr">
@@ -20508,12 +20833,12 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-007</t>
+          <t>SK-G7-AR-006</t>
         </is>
       </c>
       <c r="C153" s="18" t="inlineStr">
         <is>
-          <t>عمر أحمد عصام</t>
+          <t>بلال محمد عادل</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
@@ -20528,7 +20853,7 @@
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
@@ -20558,12 +20883,12 @@
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-AR-003</t>
+          <t>SK-G7-LN-003</t>
         </is>
       </c>
       <c r="C154" s="18" t="inlineStr">
         <is>
-          <t>فريدة شريف رجب</t>
+          <t>تقى أحمد محمود</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
@@ -20578,7 +20903,7 @@
       </c>
       <c r="F154" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G154" s="12" t="inlineStr">
@@ -20608,12 +20933,12 @@
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-AR-002</t>
+          <t>SK-G7-LN-004</t>
         </is>
       </c>
       <c r="C155" s="18" t="inlineStr">
         <is>
-          <t>ليان محمود رزق</t>
+          <t>جودى خالد رجب</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
@@ -20628,7 +20953,7 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
@@ -20658,12 +20983,12 @@
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-006</t>
+          <t>SK-G7-AR-004</t>
         </is>
       </c>
       <c r="C156" s="18" t="inlineStr">
         <is>
-          <t>مالك أدهم حربي</t>
+          <t>سارة أحمد مصطفى</t>
         </is>
       </c>
       <c r="D156" s="12" t="inlineStr">
@@ -20678,7 +21003,7 @@
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G156" s="12" t="inlineStr">
@@ -20708,12 +21033,12 @@
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-001</t>
+          <t>SK-G7-AR-005</t>
         </is>
       </c>
       <c r="C157" s="18" t="inlineStr">
         <is>
-          <t>مايا هيثم رشوان</t>
+          <t>عمار محمود سعد</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
@@ -20728,7 +21053,7 @@
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G157" s="12" t="inlineStr">
@@ -20758,12 +21083,12 @@
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-002</t>
+          <t>SK-G7-LN-007</t>
         </is>
       </c>
       <c r="C158" s="18" t="inlineStr">
         <is>
-          <t>مريم أدهم حربي</t>
+          <t>عمر أحمد عصام</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
@@ -20808,12 +21133,12 @@
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-AR-001</t>
+          <t>SK-G7-AR-003</t>
         </is>
       </c>
       <c r="C159" s="18" t="inlineStr">
         <is>
-          <t>نورسان إسلام محمد</t>
+          <t>فريدة شريف رجب</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
@@ -20858,12 +21183,12 @@
       </c>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t>SK-G7-LN-005</t>
+          <t>SK-G7-AR-002</t>
         </is>
       </c>
       <c r="C160" s="18" t="inlineStr">
         <is>
-          <t>ياسين سليمان محمد</t>
+          <t>ليان محمود رزق</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
@@ -20878,7 +21203,7 @@
       </c>
       <c r="F160" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G160" s="12" t="inlineStr">
@@ -20908,12 +21233,12 @@
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>SK-G8-LN-001</t>
+          <t>SK-G7-LN-006</t>
         </is>
       </c>
       <c r="C161" s="18" t="inlineStr">
         <is>
-          <t>بسملة عبد الله سيد</t>
+          <t>مالك أدهم حربي</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
@@ -20923,7 +21248,7 @@
       </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>الصف 8</t>
+          <t>الصف 7</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
@@ -20958,12 +21283,12 @@
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t>SK-G8-AR-002</t>
+          <t>SK-G7-LN-001</t>
         </is>
       </c>
       <c r="C162" s="18" t="inlineStr">
         <is>
-          <t>سجد محمود منصور</t>
+          <t>مايا هيثم رشوان</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
@@ -20973,12 +21298,12 @@
       </c>
       <c r="E162" s="12" t="inlineStr">
         <is>
-          <t>الصف 8</t>
+          <t>الصف 7</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G162" s="12" t="inlineStr">
@@ -21008,12 +21333,12 @@
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>SK-G8-AR-003</t>
+          <t>SK-G7-LN-002</t>
         </is>
       </c>
       <c r="C163" s="18" t="inlineStr">
         <is>
-          <t>عبد الغني عصام عبد الله</t>
+          <t>مريم أدهم حربي</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
@@ -21023,12 +21348,12 @@
       </c>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>الصف 8</t>
+          <t>الصف 7</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>عربي</t>
+          <t>لغات</t>
         </is>
       </c>
       <c r="G163" s="12" t="inlineStr">
@@ -21058,12 +21383,12 @@
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t>SK-G8-AR-001</t>
+          <t>SK-G7-AR-001</t>
         </is>
       </c>
       <c r="C164" s="18" t="inlineStr">
         <is>
-          <t>محمد حسن العمري</t>
+          <t>نورسان إسلام محمد</t>
         </is>
       </c>
       <c r="D164" s="12" t="inlineStr">
@@ -21073,7 +21398,7 @@
       </c>
       <c r="E164" s="12" t="inlineStr">
         <is>
-          <t>الصف 8</t>
+          <t>الصف 7</t>
         </is>
       </c>
       <c r="F164" s="12" t="inlineStr">
@@ -21108,12 +21433,12 @@
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>SK-G8-LN-002</t>
+          <t>SK-G7-LN-005</t>
         </is>
       </c>
       <c r="C165" s="18" t="inlineStr">
         <is>
-          <t>وتين أحمد الشوني</t>
+          <t>ياسين سليمان محمد</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
@@ -21123,7 +21448,7 @@
       </c>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>الصف 8</t>
+          <t>الصف 7</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
@@ -21158,12 +21483,12 @@
       </c>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t>SK-G9-LN-001</t>
+          <t>SK-G8-LN-001</t>
         </is>
       </c>
       <c r="C166" s="18" t="inlineStr">
         <is>
-          <t>أحمد رضا شوشة</t>
+          <t>بسملة عبد الله سيد</t>
         </is>
       </c>
       <c r="D166" s="12" t="inlineStr">
@@ -21173,7 +21498,7 @@
       </c>
       <c r="E166" s="12" t="inlineStr">
         <is>
-          <t>الصف 9</t>
+          <t>الصف 8</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
@@ -21208,12 +21533,12 @@
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>SK-G9-AR-002</t>
+          <t>SK-G8-AR-002</t>
         </is>
       </c>
       <c r="C167" s="18" t="inlineStr">
         <is>
-          <t>أيمن عصام القاضي</t>
+          <t>سجد محمود منصور</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
@@ -21223,7 +21548,7 @@
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>الصف 9</t>
+          <t>الصف 8</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
@@ -21258,12 +21583,12 @@
       </c>
       <c r="B168" s="12" t="inlineStr">
         <is>
-          <t>SK-G9-LN-002</t>
+          <t>SK-G8-AR-003</t>
         </is>
       </c>
       <c r="C168" s="18" t="inlineStr">
         <is>
-          <t>جودى هيثم رشوان</t>
+          <t>عبد الغني عصام عبد الله</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
@@ -21273,12 +21598,12 @@
       </c>
       <c r="E168" s="12" t="inlineStr">
         <is>
-          <t>الصف 9</t>
+          <t>الصف 8</t>
         </is>
       </c>
       <c r="F168" s="12" t="inlineStr">
         <is>
-          <t>لغات</t>
+          <t>عربي</t>
         </is>
       </c>
       <c r="G168" s="12" t="inlineStr">
@@ -21308,12 +21633,12 @@
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>SK-G9-AR-001</t>
+          <t>SK-G8-AR-001</t>
         </is>
       </c>
       <c r="C169" s="18" t="inlineStr">
         <is>
-          <t>ساره محمد عطاها</t>
+          <t>محمد حسن العمري</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
@@ -21323,7 +21648,7 @@
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>الصف 9</t>
+          <t>الصف 8</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
@@ -21358,45 +21683,295 @@
       </c>
       <c r="B170" s="12" t="inlineStr">
         <is>
+          <t>SK-G8-LN-002</t>
+        </is>
+      </c>
+      <c r="C170" s="18" t="inlineStr">
+        <is>
+          <t>وتين أحمد الشوني</t>
+        </is>
+      </c>
+      <c r="D170" s="12" t="inlineStr">
+        <is>
+          <t>29801011234567</t>
+        </is>
+      </c>
+      <c r="E170" s="12" t="inlineStr">
+        <is>
+          <t>الصف 8</t>
+        </is>
+      </c>
+      <c r="F170" s="12" t="inlineStr">
+        <is>
+          <t>لغات</t>
+        </is>
+      </c>
+      <c r="G170" s="12" t="inlineStr">
+        <is>
+          <t>مسلم</t>
+        </is>
+      </c>
+      <c r="H170" s="12" t="inlineStr">
+        <is>
+          <t>01000000000</t>
+        </is>
+      </c>
+      <c r="I170" s="12" t="inlineStr">
+        <is>
+          <t>مقيد ومنتظم</t>
+        </is>
+      </c>
+      <c r="J170" s="12" t="inlineStr">
+        <is>
+          <t>سجلات معتمدة 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="12" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="12" t="inlineStr">
+        <is>
+          <t>SK-G9-LN-001</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="inlineStr">
+        <is>
+          <t>أحمد رضا شوشة</t>
+        </is>
+      </c>
+      <c r="D171" s="12" t="inlineStr">
+        <is>
+          <t>29801011234567</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="inlineStr">
+        <is>
+          <t>الصف 9</t>
+        </is>
+      </c>
+      <c r="F171" s="12" t="inlineStr">
+        <is>
+          <t>لغات</t>
+        </is>
+      </c>
+      <c r="G171" s="12" t="inlineStr">
+        <is>
+          <t>مسلم</t>
+        </is>
+      </c>
+      <c r="H171" s="12" t="inlineStr">
+        <is>
+          <t>01000000000</t>
+        </is>
+      </c>
+      <c r="I171" s="12" t="inlineStr">
+        <is>
+          <t>مقيد ومنتظم</t>
+        </is>
+      </c>
+      <c r="J171" s="12" t="inlineStr">
+        <is>
+          <t>سجلات معتمدة 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="A172" s="12" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="12" t="inlineStr">
+        <is>
+          <t>SK-G9-AR-002</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="inlineStr">
+        <is>
+          <t>أيمن عصام القاضي</t>
+        </is>
+      </c>
+      <c r="D172" s="12" t="inlineStr">
+        <is>
+          <t>29801011234567</t>
+        </is>
+      </c>
+      <c r="E172" s="12" t="inlineStr">
+        <is>
+          <t>الصف 9</t>
+        </is>
+      </c>
+      <c r="F172" s="12" t="inlineStr">
+        <is>
+          <t>عربي</t>
+        </is>
+      </c>
+      <c r="G172" s="12" t="inlineStr">
+        <is>
+          <t>مسلم</t>
+        </is>
+      </c>
+      <c r="H172" s="12" t="inlineStr">
+        <is>
+          <t>01000000000</t>
+        </is>
+      </c>
+      <c r="I172" s="12" t="inlineStr">
+        <is>
+          <t>مقيد ومنتظم</t>
+        </is>
+      </c>
+      <c r="J172" s="12" t="inlineStr">
+        <is>
+          <t>سجلات معتمدة 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="A173" s="12" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="12" t="inlineStr">
+        <is>
+          <t>SK-G9-LN-002</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="inlineStr">
+        <is>
+          <t>جودى هيثم رشوان</t>
+        </is>
+      </c>
+      <c r="D173" s="12" t="inlineStr">
+        <is>
+          <t>29801011234567</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="inlineStr">
+        <is>
+          <t>الصف 9</t>
+        </is>
+      </c>
+      <c r="F173" s="12" t="inlineStr">
+        <is>
+          <t>لغات</t>
+        </is>
+      </c>
+      <c r="G173" s="12" t="inlineStr">
+        <is>
+          <t>مسلم</t>
+        </is>
+      </c>
+      <c r="H173" s="12" t="inlineStr">
+        <is>
+          <t>01000000000</t>
+        </is>
+      </c>
+      <c r="I173" s="12" t="inlineStr">
+        <is>
+          <t>مقيد ومنتظم</t>
+        </is>
+      </c>
+      <c r="J173" s="12" t="inlineStr">
+        <is>
+          <t>سجلات معتمدة 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="A174" s="12" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="12" t="inlineStr">
+        <is>
+          <t>SK-G9-AR-001</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="inlineStr">
+        <is>
+          <t>ساره محمد عطاها</t>
+        </is>
+      </c>
+      <c r="D174" s="12" t="inlineStr">
+        <is>
+          <t>29801011234567</t>
+        </is>
+      </c>
+      <c r="E174" s="12" t="inlineStr">
+        <is>
+          <t>الصف 9</t>
+        </is>
+      </c>
+      <c r="F174" s="12" t="inlineStr">
+        <is>
+          <t>عربي</t>
+        </is>
+      </c>
+      <c r="G174" s="12" t="inlineStr">
+        <is>
+          <t>مسلم</t>
+        </is>
+      </c>
+      <c r="H174" s="12" t="inlineStr">
+        <is>
+          <t>01000000000</t>
+        </is>
+      </c>
+      <c r="I174" s="12" t="inlineStr">
+        <is>
+          <t>مقيد ومنتظم</t>
+        </is>
+      </c>
+      <c r="J174" s="12" t="inlineStr">
+        <is>
+          <t>سجلات معتمدة 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="A175" s="12" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="12" t="inlineStr">
+        <is>
           <t>SK-G9-AR-003</t>
         </is>
       </c>
-      <c r="C170" s="18" t="inlineStr">
+      <c r="C175" s="18" t="inlineStr">
         <is>
           <t>محمد عبد الله النقاش</t>
         </is>
       </c>
-      <c r="D170" s="12" t="inlineStr">
+      <c r="D175" s="12" t="inlineStr">
         <is>
           <t>29801011234567</t>
         </is>
       </c>
-      <c r="E170" s="12" t="inlineStr">
+      <c r="E175" s="12" t="inlineStr">
         <is>
           <t>الصف 9</t>
         </is>
       </c>
-      <c r="F170" s="12" t="inlineStr">
+      <c r="F175" s="12" t="inlineStr">
         <is>
           <t>عربي</t>
         </is>
       </c>
-      <c r="G170" s="12" t="inlineStr">
+      <c r="G175" s="12" t="inlineStr">
         <is>
           <t>مسلم</t>
         </is>
       </c>
-      <c r="H170" s="12" t="inlineStr">
+      <c r="H175" s="12" t="inlineStr">
         <is>
           <t>01000000000</t>
         </is>
       </c>
-      <c r="I170" s="12" t="inlineStr">
+      <c r="I175" s="12" t="inlineStr">
         <is>
           <t>مقيد ومنتظم</t>
         </is>
       </c>
-      <c r="J170" s="12" t="inlineStr">
+      <c r="J175" s="12" t="inlineStr">
         <is>
           <t>سجلات معتمدة 2026</t>
         </is>
